--- a/01. Preprocessing data/data_CSV/06_Tumor.xlsx
+++ b/01. Preprocessing data/data_CSV/06_Tumor.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Аркуш1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Аркуш1!$A$1:$H$599</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4648,13 +4651,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H599"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.21875" customWidth="1"/>
+    <col min="5" max="5" width="26.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.109375" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4680,7 +4687,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -4694,7 +4701,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -4708,7 +4715,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -4725,7 +4732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
@@ -4739,7 +4746,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
@@ -4756,7 +4763,7 @@
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
@@ -4770,7 +4777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>10</v>
       </c>
@@ -4787,7 +4794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
@@ -4804,7 +4811,7 @@
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>24</v>
       </c>
@@ -4821,7 +4828,7 @@
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>26</v>
       </c>
@@ -4862,7 +4869,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>32</v>
       </c>
@@ -4879,7 +4886,7 @@
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>35</v>
       </c>
@@ -4896,7 +4903,7 @@
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>38</v>
       </c>
@@ -4913,7 +4920,7 @@
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>41</v>
       </c>
@@ -4932,7 +4939,7 @@
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>44</v>
       </c>
@@ -4949,7 +4956,7 @@
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>46</v>
       </c>
@@ -4990,7 +4997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>52</v>
       </c>
@@ -5009,7 +5016,7 @@
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>54</v>
       </c>
@@ -5028,7 +5035,7 @@
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>57</v>
       </c>
@@ -5045,7 +5052,7 @@
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>60</v>
       </c>
@@ -5086,7 +5093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>66</v>
       </c>
@@ -5103,7 +5110,7 @@
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>68</v>
       </c>
@@ -5120,7 +5127,7 @@
       <c r="F26" s="13"/>
       <c r="G26" s="13"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>71</v>
       </c>
@@ -5137,7 +5144,7 @@
       <c r="F27" s="13"/>
       <c r="G27" s="13"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>73</v>
       </c>
@@ -5154,7 +5161,7 @@
       <c r="F28" s="13"/>
       <c r="G28" s="13"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>76</v>
       </c>
@@ -5171,7 +5178,7 @@
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>78</v>
       </c>
@@ -5188,7 +5195,7 @@
       <c r="F30" s="13"/>
       <c r="G30" s="13"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>80</v>
       </c>
@@ -5205,7 +5212,7 @@
       <c r="F31" s="13"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
         <v>83</v>
       </c>
@@ -5222,7 +5229,7 @@
       <c r="F32" s="13"/>
       <c r="G32" s="13"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>85</v>
       </c>
@@ -5239,7 +5246,7 @@
       <c r="F33" s="13"/>
       <c r="G33" s="13"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>87</v>
       </c>
@@ -5258,7 +5265,7 @@
       </c>
       <c r="G34" s="13"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>90</v>
       </c>
@@ -5275,7 +5282,7 @@
       <c r="F35" s="13"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>93</v>
       </c>
@@ -5292,7 +5299,7 @@
       <c r="F36" s="13"/>
       <c r="G36" s="13"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>96</v>
       </c>
@@ -5309,7 +5316,7 @@
       <c r="F37" s="13"/>
       <c r="G37" s="13"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
         <v>99</v>
       </c>
@@ -5329,7 +5336,7 @@
       <c r="G38" s="12"/>
       <c r="H38" s="34"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>101</v>
       </c>
@@ -5346,7 +5353,7 @@
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>103</v>
       </c>
@@ -5363,7 +5370,7 @@
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
         <v>105</v>
       </c>
@@ -5380,7 +5387,7 @@
       <c r="F41" s="13"/>
       <c r="G41" s="13"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
         <v>108</v>
       </c>
@@ -5397,7 +5404,7 @@
       <c r="F42" s="13"/>
       <c r="G42" s="13"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>111</v>
       </c>
@@ -5438,7 +5445,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>116</v>
       </c>
@@ -5455,7 +5462,7 @@
       <c r="F45" s="13"/>
       <c r="G45" s="13"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>119</v>
       </c>
@@ -5472,7 +5479,7 @@
       <c r="F46" s="13"/>
       <c r="G46" s="13"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>121</v>
       </c>
@@ -5489,7 +5496,7 @@
       <c r="F47" s="13"/>
       <c r="G47" s="13"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>123</v>
       </c>
@@ -5506,7 +5513,7 @@
       <c r="F48" s="13"/>
       <c r="G48" s="13"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>125</v>
       </c>
@@ -5523,7 +5530,7 @@
       <c r="F49" s="13"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>127</v>
       </c>
@@ -5540,7 +5547,7 @@
       <c r="F50" s="13"/>
       <c r="G50" s="13"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>129</v>
       </c>
@@ -5557,7 +5564,7 @@
       <c r="F51" s="13"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>131</v>
       </c>
@@ -5574,7 +5581,7 @@
       <c r="F52" s="13"/>
       <c r="G52" s="13"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>134</v>
       </c>
@@ -5615,7 +5622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>138</v>
       </c>
@@ -5632,7 +5639,7 @@
       <c r="F55" s="13"/>
       <c r="G55" s="13"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>140</v>
       </c>
@@ -5673,7 +5680,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>145</v>
       </c>
@@ -5740,7 +5747,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="19" t="s">
         <v>154</v>
       </c>
@@ -5757,7 +5764,7 @@
       <c r="F61" s="13"/>
       <c r="G61" s="13"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>156</v>
       </c>
@@ -5774,7 +5781,7 @@
       <c r="F62" s="13"/>
       <c r="G62" s="13"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>158</v>
       </c>
@@ -5791,7 +5798,7 @@
       <c r="F63" s="13"/>
       <c r="G63" s="13"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>160</v>
       </c>
@@ -5808,7 +5815,7 @@
       <c r="F64" s="13"/>
       <c r="G64" s="13"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>163</v>
       </c>
@@ -5825,7 +5832,7 @@
       <c r="F65" s="13"/>
       <c r="G65" s="13"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>165</v>
       </c>
@@ -5842,7 +5849,7 @@
       <c r="F66" s="13"/>
       <c r="G66" s="13"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="20" t="s">
         <v>167</v>
       </c>
@@ -5859,7 +5866,7 @@
       <c r="F67" s="13"/>
       <c r="G67" s="13"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>169</v>
       </c>
@@ -5876,7 +5883,7 @@
       <c r="F68" s="13"/>
       <c r="G68" s="13"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="10" t="s">
         <v>171</v>
       </c>
@@ -5893,7 +5900,7 @@
       <c r="F69" s="13"/>
       <c r="G69" s="13"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>174</v>
       </c>
@@ -5912,7 +5919,7 @@
       <c r="F70" s="13"/>
       <c r="G70" s="13"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>176</v>
       </c>
@@ -5929,7 +5936,7 @@
       <c r="F71" s="13"/>
       <c r="G71" s="13"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>178</v>
       </c>
@@ -5946,7 +5953,7 @@
       <c r="F72" s="13"/>
       <c r="G72" s="13"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>180</v>
       </c>
@@ -5963,7 +5970,7 @@
       <c r="F73" s="13"/>
       <c r="G73" s="13"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>182</v>
       </c>
@@ -5980,7 +5987,7 @@
       <c r="F74" s="13"/>
       <c r="G74" s="13"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>184</v>
       </c>
@@ -5997,7 +6004,7 @@
       <c r="F75" s="13"/>
       <c r="G75" s="13"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>186</v>
       </c>
@@ -6014,7 +6021,7 @@
       <c r="F76" s="13"/>
       <c r="G76" s="13"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>188</v>
       </c>
@@ -6031,7 +6038,7 @@
       <c r="F77" s="13"/>
       <c r="G77" s="13"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>190</v>
       </c>
@@ -6072,7 +6079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>195</v>
       </c>
@@ -6089,7 +6096,7 @@
       <c r="F80" s="13"/>
       <c r="G80" s="13"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>197</v>
       </c>
@@ -6106,7 +6113,7 @@
       <c r="F81" s="13"/>
       <c r="G81" s="13"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>199</v>
       </c>
@@ -6123,7 +6130,7 @@
       <c r="F82" s="13"/>
       <c r="G82" s="13"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>201</v>
       </c>
@@ -6140,7 +6147,7 @@
       <c r="F83" s="13"/>
       <c r="G83" s="13"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>203</v>
       </c>
@@ -6157,7 +6164,7 @@
       <c r="F84" s="13"/>
       <c r="G84" s="13"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>206</v>
       </c>
@@ -6174,7 +6181,7 @@
       <c r="F85" s="13"/>
       <c r="G85" s="13"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="19" t="s">
         <v>209</v>
       </c>
@@ -6236,7 +6243,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
         <v>215</v>
       </c>
@@ -6255,7 +6262,7 @@
       <c r="F89" s="13"/>
       <c r="G89" s="13"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>218</v>
       </c>
@@ -6272,7 +6279,7 @@
       <c r="F90" s="13"/>
       <c r="G90" s="13"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
         <v>220</v>
       </c>
@@ -6291,7 +6298,7 @@
       </c>
       <c r="G91" s="13"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>222</v>
       </c>
@@ -6308,7 +6315,7 @@
       <c r="F92" s="13"/>
       <c r="G92" s="13"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>224</v>
       </c>
@@ -6325,7 +6332,7 @@
       <c r="F93" s="13"/>
       <c r="G93" s="13"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>226</v>
       </c>
@@ -6342,7 +6349,7 @@
       <c r="F94" s="13"/>
       <c r="G94" s="13"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>228</v>
       </c>
@@ -6407,7 +6414,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="10" t="s">
         <v>235</v>
       </c>
@@ -6424,7 +6431,7 @@
       <c r="F98" s="13"/>
       <c r="G98" s="13"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>238</v>
       </c>
@@ -6441,7 +6448,7 @@
       <c r="F99" s="13"/>
       <c r="G99" s="13"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -6458,7 +6465,7 @@
       <c r="F100" s="13"/>
       <c r="G100" s="13"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -6475,7 +6482,7 @@
       <c r="F101" s="13"/>
       <c r="G101" s="13"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="13" t="s">
         <v>244</v>
       </c>
@@ -6492,7 +6499,7 @@
       <c r="F102" s="13"/>
       <c r="G102" s="13"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="13" t="s">
         <v>246</v>
       </c>
@@ -6509,7 +6516,7 @@
       <c r="F103" s="13"/>
       <c r="G103" s="13"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
         <v>248</v>
       </c>
@@ -6528,7 +6535,7 @@
       <c r="F104" s="13"/>
       <c r="G104" s="13"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="13" t="s">
         <v>250</v>
       </c>
@@ -6545,7 +6552,7 @@
       <c r="F105" s="13"/>
       <c r="G105" s="13"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="13" t="s">
         <v>252</v>
       </c>
@@ -6562,7 +6569,7 @@
       <c r="F106" s="13"/>
       <c r="G106" s="13"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="13" t="s">
         <v>255</v>
       </c>
@@ -6579,7 +6586,7 @@
       <c r="F107" s="13"/>
       <c r="G107" s="13"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="13" t="s">
         <v>257</v>
       </c>
@@ -6596,7 +6603,7 @@
       <c r="F108" s="13"/>
       <c r="G108" s="13"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="13" t="s">
         <v>260</v>
       </c>
@@ -6613,7 +6620,7 @@
       <c r="F109" s="13"/>
       <c r="G109" s="13"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="13" t="s">
         <v>262</v>
       </c>
@@ -6630,7 +6637,7 @@
       <c r="F110" s="13"/>
       <c r="G110" s="13"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="13" t="s">
         <v>264</v>
       </c>
@@ -6647,7 +6654,7 @@
       <c r="F111" s="13"/>
       <c r="G111" s="13"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="13" t="s">
         <v>266</v>
       </c>
@@ -6664,7 +6671,7 @@
       <c r="F112" s="13"/>
       <c r="G112" s="13"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
         <v>268</v>
       </c>
@@ -6681,7 +6688,7 @@
       <c r="F113" s="13"/>
       <c r="G113" s="13"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
         <v>271</v>
       </c>
@@ -6698,7 +6705,7 @@
       <c r="F114" s="13"/>
       <c r="G114" s="13"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="13" t="s">
         <v>273</v>
       </c>
@@ -6715,7 +6722,7 @@
       <c r="F115" s="13"/>
       <c r="G115" s="13"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="13" t="s">
         <v>276</v>
       </c>
@@ -6732,7 +6739,7 @@
       <c r="F116" s="13"/>
       <c r="G116" s="13"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="13" t="s">
         <v>279</v>
       </c>
@@ -6749,7 +6756,7 @@
       <c r="F117" s="13"/>
       <c r="G117" s="13"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="13" t="s">
         <v>282</v>
       </c>
@@ -6766,7 +6773,7 @@
       <c r="F118" s="13"/>
       <c r="G118" s="13"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="13" t="s">
         <v>284</v>
       </c>
@@ -6783,7 +6790,7 @@
       <c r="F119" s="13"/>
       <c r="G119" s="13"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="13" t="s">
         <v>286</v>
       </c>
@@ -6800,7 +6807,7 @@
       <c r="F120" s="13"/>
       <c r="G120" s="13"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="13" t="s">
         <v>288</v>
       </c>
@@ -6817,7 +6824,7 @@
       <c r="F121" s="13"/>
       <c r="G121" s="13"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="13" t="s">
         <v>290</v>
       </c>
@@ -6834,7 +6841,7 @@
       <c r="F122" s="13"/>
       <c r="G122" s="13"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="13" t="s">
         <v>292</v>
       </c>
@@ -6875,7 +6882,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="13" t="s">
         <v>296</v>
       </c>
@@ -6892,7 +6899,7 @@
       <c r="F125" s="13"/>
       <c r="G125" s="13"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="13" t="s">
         <v>299</v>
       </c>
@@ -6909,7 +6916,7 @@
       <c r="F126" s="13"/>
       <c r="G126" s="13"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="13" t="s">
         <v>301</v>
       </c>
@@ -6926,7 +6933,7 @@
       <c r="F127" s="13"/>
       <c r="G127" s="13"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="13" t="s">
         <v>303</v>
       </c>
@@ -6943,7 +6950,7 @@
       <c r="F128" s="13"/>
       <c r="G128" s="13"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="13" t="s">
         <v>305</v>
       </c>
@@ -6960,7 +6967,7 @@
       <c r="F129" s="13"/>
       <c r="G129" s="13"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="13" t="s">
         <v>307</v>
       </c>
@@ -6977,7 +6984,7 @@
       <c r="F130" s="13"/>
       <c r="G130" s="13"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="13" t="s">
         <v>309</v>
       </c>
@@ -6994,7 +7001,7 @@
       <c r="F131" s="13"/>
       <c r="G131" s="13"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="22" t="s">
         <v>311</v>
       </c>
@@ -7013,7 +7020,7 @@
       <c r="F132" s="13"/>
       <c r="G132" s="13"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="13" t="s">
         <v>313</v>
       </c>
@@ -7030,7 +7037,7 @@
       <c r="F133" s="13"/>
       <c r="G133" s="13"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="13" t="s">
         <v>315</v>
       </c>
@@ -7047,7 +7054,7 @@
       <c r="F134" s="13"/>
       <c r="G134" s="13"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="13" t="s">
         <v>317</v>
       </c>
@@ -7064,7 +7071,7 @@
       <c r="F135" s="13"/>
       <c r="G135" s="13"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="13" t="s">
         <v>319</v>
       </c>
@@ -7107,7 +7114,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="13" t="s">
         <v>324</v>
       </c>
@@ -7124,7 +7131,7 @@
       <c r="F138" s="13"/>
       <c r="G138" s="13"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="13" t="s">
         <v>327</v>
       </c>
@@ -7141,7 +7148,7 @@
       <c r="F139" s="13"/>
       <c r="G139" s="13"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="13" t="s">
         <v>329</v>
       </c>
@@ -7158,7 +7165,7 @@
       <c r="F140" s="13"/>
       <c r="G140" s="13"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="13" t="s">
         <v>332</v>
       </c>
@@ -7175,7 +7182,7 @@
       <c r="F141" s="13"/>
       <c r="G141" s="13"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="13" t="s">
         <v>335</v>
       </c>
@@ -7192,7 +7199,7 @@
       <c r="F142" s="13"/>
       <c r="G142" s="13"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
         <v>338</v>
       </c>
@@ -7211,7 +7218,7 @@
       <c r="F143" s="13"/>
       <c r="G143" s="13"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="13" t="s">
         <v>340</v>
       </c>
@@ -7228,7 +7235,7 @@
       <c r="F144" s="13"/>
       <c r="G144" s="13"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="13" t="s">
         <v>342</v>
       </c>
@@ -7245,7 +7252,7 @@
       <c r="F145" s="13"/>
       <c r="G145" s="13"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6" t="s">
         <v>344</v>
       </c>
@@ -7264,7 +7271,7 @@
       <c r="F146" s="13"/>
       <c r="G146" s="13"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="13" t="s">
         <v>346</v>
       </c>
@@ -7281,7 +7288,7 @@
       <c r="F147" s="13"/>
       <c r="G147" s="13"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="13" t="s">
         <v>348</v>
       </c>
@@ -7298,7 +7305,7 @@
       <c r="F148" s="13"/>
       <c r="G148" s="13"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="13" t="s">
         <v>351</v>
       </c>
@@ -7315,7 +7322,7 @@
       <c r="F149" s="13"/>
       <c r="G149" s="13"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="13" t="s">
         <v>353</v>
       </c>
@@ -7332,7 +7339,7 @@
       <c r="F150" s="13"/>
       <c r="G150" s="13"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="13" t="s">
         <v>355</v>
       </c>
@@ -7349,7 +7356,7 @@
       <c r="F151" s="13"/>
       <c r="G151" s="13"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="13" t="s">
         <v>357</v>
       </c>
@@ -7366,7 +7373,7 @@
       <c r="F152" s="13"/>
       <c r="G152" s="13"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="13" t="s">
         <v>359</v>
       </c>
@@ -7385,7 +7392,7 @@
       <c r="F153" s="13"/>
       <c r="G153" s="13"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="13" t="s">
         <v>361</v>
       </c>
@@ -7402,7 +7409,7 @@
       <c r="F154" s="13"/>
       <c r="G154" s="13"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="13" t="s">
         <v>363</v>
       </c>
@@ -7419,7 +7426,7 @@
       <c r="F155" s="13"/>
       <c r="G155" s="13"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="13" t="s">
         <v>365</v>
       </c>
@@ -7436,7 +7443,7 @@
       <c r="F156" s="13"/>
       <c r="G156" s="13"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="13" t="s">
         <v>367</v>
       </c>
@@ -7453,7 +7460,7 @@
       <c r="F157" s="13"/>
       <c r="G157" s="13"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="13" t="s">
         <v>369</v>
       </c>
@@ -7470,7 +7477,7 @@
       <c r="F158" s="13"/>
       <c r="G158" s="13"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="13" t="s">
         <v>371</v>
       </c>
@@ -7487,7 +7494,7 @@
       <c r="F159" s="13"/>
       <c r="G159" s="13"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="13" t="s">
         <v>373</v>
       </c>
@@ -7504,7 +7511,7 @@
       <c r="F160" s="13"/>
       <c r="G160" s="13"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="13" t="s">
         <v>376</v>
       </c>
@@ -7521,7 +7528,7 @@
       <c r="F161" s="13"/>
       <c r="G161" s="13"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="13" t="s">
         <v>378</v>
       </c>
@@ -7538,7 +7545,7 @@
       <c r="F162" s="13"/>
       <c r="G162" s="13"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="13" t="s">
         <v>380</v>
       </c>
@@ -7579,7 +7586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="13" t="s">
         <v>384</v>
       </c>
@@ -7596,7 +7603,7 @@
       <c r="F165" s="13"/>
       <c r="G165" s="13"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="13" t="s">
         <v>386</v>
       </c>
@@ -7613,7 +7620,7 @@
       <c r="F166" s="13"/>
       <c r="G166" s="13"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="10" t="s">
         <v>388</v>
       </c>
@@ -7630,7 +7637,7 @@
       <c r="F167" s="13"/>
       <c r="G167" s="13"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="13" t="s">
         <v>391</v>
       </c>
@@ -7647,7 +7654,7 @@
       <c r="F168" s="13"/>
       <c r="G168" s="13"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="13" t="s">
         <v>393</v>
       </c>
@@ -7664,7 +7671,7 @@
       <c r="F169" s="13"/>
       <c r="G169" s="13"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="13" t="s">
         <v>395</v>
       </c>
@@ -7681,7 +7688,7 @@
       <c r="F170" s="13"/>
       <c r="G170" s="13"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="13" t="s">
         <v>397</v>
       </c>
@@ -7698,7 +7705,7 @@
       <c r="F171" s="13"/>
       <c r="G171" s="13"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="13" t="s">
         <v>399</v>
       </c>
@@ -7715,7 +7722,7 @@
       <c r="F172" s="13"/>
       <c r="G172" s="13"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="13" t="s">
         <v>401</v>
       </c>
@@ -7732,7 +7739,7 @@
       <c r="F173" s="13"/>
       <c r="G173" s="13"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="13" t="s">
         <v>403</v>
       </c>
@@ -7749,7 +7756,7 @@
       <c r="F174" s="13"/>
       <c r="G174" s="13"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="13" t="s">
         <v>405</v>
       </c>
@@ -7766,7 +7773,7 @@
       <c r="F175" s="13"/>
       <c r="G175" s="13"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="13" t="s">
         <v>407</v>
       </c>
@@ -7783,7 +7790,7 @@
       <c r="F176" s="13"/>
       <c r="G176" s="13"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="13" t="s">
         <v>409</v>
       </c>
@@ -7802,7 +7809,7 @@
       <c r="F177" s="13"/>
       <c r="G177" s="13"/>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="13" t="s">
         <v>411</v>
       </c>
@@ -7819,7 +7826,7 @@
       <c r="F178" s="13"/>
       <c r="G178" s="13"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="13" t="s">
         <v>413</v>
       </c>
@@ -7838,7 +7845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="13" t="s">
         <v>415</v>
       </c>
@@ -7857,7 +7864,7 @@
       <c r="F180" s="13"/>
       <c r="G180" s="13"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="13" t="s">
         <v>418</v>
       </c>
@@ -7874,7 +7881,7 @@
       <c r="F181" s="13"/>
       <c r="G181" s="13"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="13" t="s">
         <v>421</v>
       </c>
@@ -7891,7 +7898,7 @@
       <c r="F182" s="13"/>
       <c r="G182" s="13"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="13" t="s">
         <v>423</v>
       </c>
@@ -7908,7 +7915,7 @@
       <c r="F183" s="13"/>
       <c r="G183" s="13"/>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="13" t="s">
         <v>425</v>
       </c>
@@ -7925,7 +7932,7 @@
       <c r="F184" s="13"/>
       <c r="G184" s="13"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="13" t="s">
         <v>427</v>
       </c>
@@ -7942,7 +7949,7 @@
       <c r="F185" s="13"/>
       <c r="G185" s="13"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="13" t="s">
         <v>429</v>
       </c>
@@ -7959,7 +7966,7 @@
       <c r="F186" s="13"/>
       <c r="G186" s="13"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="13" t="s">
         <v>431</v>
       </c>
@@ -7976,7 +7983,7 @@
       <c r="F187" s="13"/>
       <c r="G187" s="13"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="10" t="s">
         <v>433</v>
       </c>
@@ -7993,7 +8000,7 @@
       <c r="F188" s="13"/>
       <c r="G188" s="13"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="13" t="s">
         <v>435</v>
       </c>
@@ -8010,7 +8017,7 @@
       <c r="F189" s="13"/>
       <c r="G189" s="13"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="13" t="s">
         <v>437</v>
       </c>
@@ -8027,7 +8034,7 @@
       <c r="F190" s="13"/>
       <c r="G190" s="13"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="13" t="s">
         <v>439</v>
       </c>
@@ -8044,7 +8051,7 @@
       <c r="F191" s="13"/>
       <c r="G191" s="13"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="13" t="s">
         <v>441</v>
       </c>
@@ -8061,7 +8068,7 @@
       <c r="F192" s="13"/>
       <c r="G192" s="13"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="13" t="s">
         <v>443</v>
       </c>
@@ -8078,7 +8085,7 @@
       <c r="F193" s="13"/>
       <c r="G193" s="13"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="13" t="s">
         <v>445</v>
       </c>
@@ -8097,7 +8104,7 @@
       <c r="F194" s="13"/>
       <c r="G194" s="13"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="13" t="s">
         <v>447</v>
       </c>
@@ -8114,7 +8121,7 @@
       <c r="F195" s="13"/>
       <c r="G195" s="13"/>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="24" t="s">
         <v>449</v>
       </c>
@@ -8133,7 +8140,7 @@
       <c r="F196" s="13"/>
       <c r="G196" s="13"/>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="13" t="s">
         <v>451</v>
       </c>
@@ -8150,7 +8157,7 @@
       <c r="F197" s="13"/>
       <c r="G197" s="13"/>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6" t="s">
         <v>453</v>
       </c>
@@ -8193,7 +8200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="13" t="s">
         <v>458</v>
       </c>
@@ -8212,7 +8219,7 @@
       <c r="F200" s="13"/>
       <c r="G200" s="13"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="13" t="s">
         <v>460</v>
       </c>
@@ -8229,7 +8236,7 @@
       <c r="F201" s="13"/>
       <c r="G201" s="13"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="13" t="s">
         <v>462</v>
       </c>
@@ -8246,7 +8253,7 @@
       <c r="F202" s="13"/>
       <c r="G202" s="13"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="13" t="s">
         <v>464</v>
       </c>
@@ -8263,7 +8270,7 @@
       <c r="F203" s="13"/>
       <c r="G203" s="13"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="13" t="s">
         <v>467</v>
       </c>
@@ -8280,7 +8287,7 @@
       <c r="F204" s="13"/>
       <c r="G204" s="13"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6" t="s">
         <v>469</v>
       </c>
@@ -8299,7 +8306,7 @@
       <c r="F205" s="13"/>
       <c r="G205" s="13"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="13" t="s">
         <v>472</v>
       </c>
@@ -8316,7 +8323,7 @@
       <c r="F206" s="13"/>
       <c r="G206" s="13"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="13" t="s">
         <v>474</v>
       </c>
@@ -8333,7 +8340,7 @@
       <c r="F207" s="13"/>
       <c r="G207" s="13"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="13" t="s">
         <v>476</v>
       </c>
@@ -8350,7 +8357,7 @@
       <c r="F208" s="13"/>
       <c r="G208" s="13"/>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="13" t="s">
         <v>478</v>
       </c>
@@ -8367,7 +8374,7 @@
       <c r="F209" s="13"/>
       <c r="G209" s="13"/>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="13" t="s">
         <v>480</v>
       </c>
@@ -8384,7 +8391,7 @@
       <c r="F210" s="13"/>
       <c r="G210" s="13"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="13" t="s">
         <v>482</v>
       </c>
@@ -8401,7 +8408,7 @@
       <c r="F211" s="13"/>
       <c r="G211" s="13"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="13" t="s">
         <v>484</v>
       </c>
@@ -8418,7 +8425,7 @@
       <c r="F212" s="13"/>
       <c r="G212" s="13"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="13" t="s">
         <v>486</v>
       </c>
@@ -8435,7 +8442,7 @@
       <c r="F213" s="13"/>
       <c r="G213" s="13"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="13" t="s">
         <v>488</v>
       </c>
@@ -8476,7 +8483,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="13" t="s">
         <v>492</v>
       </c>
@@ -8493,7 +8500,7 @@
       <c r="F216" s="13"/>
       <c r="G216" s="13"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="13" t="s">
         <v>495</v>
       </c>
@@ -8510,7 +8517,7 @@
       <c r="F217" s="13"/>
       <c r="G217" s="13"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="13" t="s">
         <v>497</v>
       </c>
@@ -8527,7 +8534,7 @@
       <c r="F218" s="13"/>
       <c r="G218" s="13"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="13" t="s">
         <v>499</v>
       </c>
@@ -8544,7 +8551,7 @@
       <c r="F219" s="13"/>
       <c r="G219" s="13"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="13" t="s">
         <v>501</v>
       </c>
@@ -8561,7 +8568,7 @@
       <c r="F220" s="13"/>
       <c r="G220" s="13"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="13" t="s">
         <v>503</v>
       </c>
@@ -8578,7 +8585,7 @@
       <c r="F221" s="13"/>
       <c r="G221" s="13"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="13" t="s">
         <v>505</v>
       </c>
@@ -8595,7 +8602,7 @@
       <c r="F222" s="13"/>
       <c r="G222" s="13"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="13" t="s">
         <v>507</v>
       </c>
@@ -8612,7 +8619,7 @@
       <c r="F223" s="13"/>
       <c r="G223" s="13"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="13" t="s">
         <v>509</v>
       </c>
@@ -8629,7 +8636,7 @@
       <c r="F224" s="13"/>
       <c r="G224" s="13"/>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="13" t="s">
         <v>511</v>
       </c>
@@ -8646,7 +8653,7 @@
       <c r="F225" s="13"/>
       <c r="G225" s="13"/>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="13" t="s">
         <v>513</v>
       </c>
@@ -8663,7 +8670,7 @@
       <c r="F226" s="13"/>
       <c r="G226" s="13"/>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="13" t="s">
         <v>515</v>
       </c>
@@ -8680,7 +8687,7 @@
       <c r="F227" s="13"/>
       <c r="G227" s="13"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="13" t="s">
         <v>517</v>
       </c>
@@ -8697,7 +8704,7 @@
       <c r="F228" s="13"/>
       <c r="G228" s="13"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="13" t="s">
         <v>519</v>
       </c>
@@ -8738,7 +8745,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="13" t="s">
         <v>525</v>
       </c>
@@ -8755,7 +8762,7 @@
       <c r="F231" s="13"/>
       <c r="G231" s="13"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="13" t="s">
         <v>527</v>
       </c>
@@ -8772,7 +8779,7 @@
       <c r="F232" s="13"/>
       <c r="G232" s="13"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="13" t="s">
         <v>529</v>
       </c>
@@ -8789,7 +8796,7 @@
       <c r="F233" s="13"/>
       <c r="G233" s="13"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="13" t="s">
         <v>531</v>
       </c>
@@ -8806,7 +8813,7 @@
       <c r="F234" s="13"/>
       <c r="G234" s="13"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="13" t="s">
         <v>533</v>
       </c>
@@ -8823,7 +8830,7 @@
       <c r="F235" s="13"/>
       <c r="G235" s="13"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="13" t="s">
         <v>535</v>
       </c>
@@ -8840,7 +8847,7 @@
       <c r="F236" s="13"/>
       <c r="G236" s="13"/>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="13" t="s">
         <v>537</v>
       </c>
@@ -8881,7 +8888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="13" t="s">
         <v>541</v>
       </c>
@@ -8898,7 +8905,7 @@
       <c r="F239" s="13"/>
       <c r="G239" s="13"/>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="13" t="s">
         <v>543</v>
       </c>
@@ -8939,7 +8946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="13" t="s">
         <v>547</v>
       </c>
@@ -8956,7 +8963,7 @@
       <c r="F242" s="13"/>
       <c r="G242" s="13"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="13" t="s">
         <v>549</v>
       </c>
@@ -8973,7 +8980,7 @@
       <c r="F243" s="13"/>
       <c r="G243" s="13"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="13" t="s">
         <v>551</v>
       </c>
@@ -8990,7 +8997,7 @@
       <c r="F244" s="13"/>
       <c r="G244" s="13"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="13" t="s">
         <v>553</v>
       </c>
@@ -9007,7 +9014,7 @@
       <c r="F245" s="13"/>
       <c r="G245" s="13"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="13" t="s">
         <v>555</v>
       </c>
@@ -9024,7 +9031,7 @@
       <c r="F246" s="13"/>
       <c r="G246" s="13"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="13" t="s">
         <v>558</v>
       </c>
@@ -9041,7 +9048,7 @@
       <c r="F247" s="13"/>
       <c r="G247" s="13"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="13" t="s">
         <v>560</v>
       </c>
@@ -9058,7 +9065,7 @@
       <c r="F248" s="13"/>
       <c r="G248" s="13"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="13" t="s">
         <v>563</v>
       </c>
@@ -9075,7 +9082,7 @@
       <c r="F249" s="13"/>
       <c r="G249" s="13"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="13" t="s">
         <v>566</v>
       </c>
@@ -9140,7 +9147,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="13" t="s">
         <v>575</v>
       </c>
@@ -9157,7 +9164,7 @@
       <c r="F253" s="13"/>
       <c r="G253" s="13"/>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="13" t="s">
         <v>577</v>
       </c>
@@ -9174,7 +9181,7 @@
       <c r="F254" s="13"/>
       <c r="G254" s="13"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="13" t="s">
         <v>579</v>
       </c>
@@ -9191,7 +9198,7 @@
       <c r="F255" s="13"/>
       <c r="G255" s="13"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="13" t="s">
         <v>581</v>
       </c>
@@ -9208,7 +9215,7 @@
       <c r="F256" s="13"/>
       <c r="G256" s="13"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="13" t="s">
         <v>583</v>
       </c>
@@ -9225,7 +9232,7 @@
       <c r="F257" s="13"/>
       <c r="G257" s="13"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="13" t="s">
         <v>585</v>
       </c>
@@ -9242,7 +9249,7 @@
       <c r="F258" s="13"/>
       <c r="G258" s="13"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="13" t="s">
         <v>587</v>
       </c>
@@ -9259,7 +9266,7 @@
       <c r="F259" s="13"/>
       <c r="G259" s="13"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="13" t="s">
         <v>589</v>
       </c>
@@ -9300,7 +9307,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="13" t="s">
         <v>593</v>
       </c>
@@ -9317,7 +9324,7 @@
       <c r="F262" s="13"/>
       <c r="G262" s="13"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="13" t="s">
         <v>595</v>
       </c>
@@ -9334,7 +9341,7 @@
       <c r="F263" s="13"/>
       <c r="G263" s="13"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="13" t="s">
         <v>597</v>
       </c>
@@ -9351,7 +9358,7 @@
       <c r="F264" s="13"/>
       <c r="G264" s="13"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="13" t="s">
         <v>599</v>
       </c>
@@ -9368,7 +9375,7 @@
       <c r="F265" s="13"/>
       <c r="G265" s="13"/>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="13" t="s">
         <v>601</v>
       </c>
@@ -9385,7 +9392,7 @@
       <c r="F266" s="13"/>
       <c r="G266" s="13"/>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="13" t="s">
         <v>604</v>
       </c>
@@ -9402,7 +9409,7 @@
       <c r="F267" s="13"/>
       <c r="G267" s="13"/>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="13" t="s">
         <v>606</v>
       </c>
@@ -9419,7 +9426,7 @@
       <c r="F268" s="13"/>
       <c r="G268" s="13"/>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="13" t="s">
         <v>608</v>
       </c>
@@ -9436,7 +9443,7 @@
       <c r="F269" s="13"/>
       <c r="G269" s="13"/>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="13" t="s">
         <v>610</v>
       </c>
@@ -9477,7 +9484,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="13" t="s">
         <v>614</v>
       </c>
@@ -9494,7 +9501,7 @@
       <c r="F272" s="13"/>
       <c r="G272" s="13"/>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="13" t="s">
         <v>616</v>
       </c>
@@ -9511,7 +9518,7 @@
       <c r="F273" s="13"/>
       <c r="G273" s="13"/>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="13" t="s">
         <v>618</v>
       </c>
@@ -9552,7 +9559,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="13" t="s">
         <v>623</v>
       </c>
@@ -9569,7 +9576,7 @@
       <c r="F276" s="13"/>
       <c r="G276" s="13"/>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="13" t="s">
         <v>625</v>
       </c>
@@ -9586,7 +9593,7 @@
       <c r="F277" s="13"/>
       <c r="G277" s="13"/>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="13" t="s">
         <v>628</v>
       </c>
@@ -9603,7 +9610,7 @@
       <c r="F278" s="13"/>
       <c r="G278" s="13"/>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="13" t="s">
         <v>630</v>
       </c>
@@ -9620,7 +9627,7 @@
       <c r="F279" s="13"/>
       <c r="G279" s="13"/>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="13" t="s">
         <v>632</v>
       </c>
@@ -9637,7 +9644,7 @@
       <c r="F280" s="13"/>
       <c r="G280" s="13"/>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="13" t="s">
         <v>634</v>
       </c>
@@ -9654,7 +9661,7 @@
       <c r="F281" s="13"/>
       <c r="G281" s="13"/>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="13" t="s">
         <v>636</v>
       </c>
@@ -9671,7 +9678,7 @@
       <c r="F282" s="13"/>
       <c r="G282" s="13"/>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="13" t="s">
         <v>638</v>
       </c>
@@ -9688,7 +9695,7 @@
       <c r="F283" s="13"/>
       <c r="G283" s="13"/>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="13" t="s">
         <v>640</v>
       </c>
@@ -9705,7 +9712,7 @@
       <c r="F284" s="13"/>
       <c r="G284" s="13"/>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="13" t="s">
         <v>642</v>
       </c>
@@ -9722,7 +9729,7 @@
       <c r="F285" s="13"/>
       <c r="G285" s="13"/>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="13" t="s">
         <v>644</v>
       </c>
@@ -9739,7 +9746,7 @@
       <c r="F286" s="13"/>
       <c r="G286" s="13"/>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="25" t="s">
         <v>646</v>
       </c>
@@ -9756,7 +9763,7 @@
       <c r="F287" s="13"/>
       <c r="G287" s="13"/>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="13" t="s">
         <v>648</v>
       </c>
@@ -9773,7 +9780,7 @@
       <c r="F288" s="13"/>
       <c r="G288" s="13"/>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="13" t="s">
         <v>651</v>
       </c>
@@ -9790,7 +9797,7 @@
       <c r="F289" s="13"/>
       <c r="G289" s="13"/>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="13" t="s">
         <v>653</v>
       </c>
@@ -9807,7 +9814,7 @@
       <c r="F290" s="13"/>
       <c r="G290" s="13"/>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="13" t="s">
         <v>655</v>
       </c>
@@ -9824,7 +9831,7 @@
       <c r="F291" s="13"/>
       <c r="G291" s="13"/>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="13" t="s">
         <v>657</v>
       </c>
@@ -9841,7 +9848,7 @@
       <c r="F292" s="13"/>
       <c r="G292" s="13"/>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="13" t="s">
         <v>660</v>
       </c>
@@ -9858,7 +9865,7 @@
       <c r="F293" s="13"/>
       <c r="G293" s="13"/>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="13" t="s">
         <v>662</v>
       </c>
@@ -9875,7 +9882,7 @@
       <c r="F294" s="13"/>
       <c r="G294" s="13"/>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="13" t="s">
         <v>664</v>
       </c>
@@ -9892,7 +9899,7 @@
       <c r="F295" s="13"/>
       <c r="G295" s="13"/>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="13" t="s">
         <v>666</v>
       </c>
@@ -9909,7 +9916,7 @@
       <c r="F296" s="13"/>
       <c r="G296" s="13"/>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="13" t="s">
         <v>668</v>
       </c>
@@ -9926,7 +9933,7 @@
       <c r="F297" s="13"/>
       <c r="G297" s="13"/>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="13" t="s">
         <v>671</v>
       </c>
@@ -9943,7 +9950,7 @@
       <c r="F298" s="13"/>
       <c r="G298" s="13"/>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="13" t="s">
         <v>673</v>
       </c>
@@ -9960,7 +9967,7 @@
       <c r="F299" s="13"/>
       <c r="G299" s="13"/>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="13" t="s">
         <v>676</v>
       </c>
@@ -9977,7 +9984,7 @@
       <c r="F300" s="13"/>
       <c r="G300" s="13"/>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="13" t="s">
         <v>678</v>
       </c>
@@ -9994,7 +10001,7 @@
       <c r="F301" s="13"/>
       <c r="G301" s="13"/>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="13" t="s">
         <v>681</v>
       </c>
@@ -10011,7 +10018,7 @@
       <c r="F302" s="13"/>
       <c r="G302" s="13"/>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="13" t="s">
         <v>683</v>
       </c>
@@ -10028,7 +10035,7 @@
       <c r="F303" s="13"/>
       <c r="G303" s="13"/>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="13" t="s">
         <v>685</v>
       </c>
@@ -10045,7 +10052,7 @@
       <c r="F304" s="13"/>
       <c r="G304" s="13"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="13" t="s">
         <v>687</v>
       </c>
@@ -10062,7 +10069,7 @@
       <c r="F305" s="13"/>
       <c r="G305" s="13"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="13" t="s">
         <v>689</v>
       </c>
@@ -10079,7 +10086,7 @@
       <c r="F306" s="13"/>
       <c r="G306" s="13"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="13" t="s">
         <v>691</v>
       </c>
@@ -10096,7 +10103,7 @@
       <c r="F307" s="13"/>
       <c r="G307" s="13"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="13" t="s">
         <v>693</v>
       </c>
@@ -10113,7 +10120,7 @@
       <c r="F308" s="13"/>
       <c r="G308" s="13"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="10" t="s">
         <v>695</v>
       </c>
@@ -10130,7 +10137,7 @@
       <c r="F309" s="13"/>
       <c r="G309" s="13"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="13" t="s">
         <v>697</v>
       </c>
@@ -10147,7 +10154,7 @@
       <c r="F310" s="13"/>
       <c r="G310" s="13"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="13" t="s">
         <v>699</v>
       </c>
@@ -10188,7 +10195,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="13" t="s">
         <v>703</v>
       </c>
@@ -10205,7 +10212,7 @@
       <c r="F313" s="13"/>
       <c r="G313" s="13"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="13" t="s">
         <v>705</v>
       </c>
@@ -10222,7 +10229,7 @@
       <c r="F314" s="13"/>
       <c r="G314" s="13"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="13" t="s">
         <v>707</v>
       </c>
@@ -10239,7 +10246,7 @@
       <c r="F315" s="13"/>
       <c r="G315" s="13"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="13" t="s">
         <v>710</v>
       </c>
@@ -10256,7 +10263,7 @@
       <c r="F316" s="13"/>
       <c r="G316" s="13"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="13" t="s">
         <v>712</v>
       </c>
@@ -10273,7 +10280,7 @@
       <c r="F317" s="13"/>
       <c r="G317" s="13"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="13" t="s">
         <v>715</v>
       </c>
@@ -10290,7 +10297,7 @@
       <c r="F318" s="13"/>
       <c r="G318" s="13"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="13" t="s">
         <v>717</v>
       </c>
@@ -10307,7 +10314,7 @@
       <c r="F319" s="13"/>
       <c r="G319" s="13"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="13" t="s">
         <v>719</v>
       </c>
@@ -10324,7 +10331,7 @@
       <c r="F320" s="13"/>
       <c r="G320" s="13"/>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="13" t="s">
         <v>721</v>
       </c>
@@ -10341,7 +10348,7 @@
       <c r="F321" s="13"/>
       <c r="G321" s="13"/>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="13" t="s">
         <v>723</v>
       </c>
@@ -10358,7 +10365,7 @@
       <c r="F322" s="13"/>
       <c r="G322" s="13"/>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="13" t="s">
         <v>725</v>
       </c>
@@ -10375,7 +10382,7 @@
       <c r="F323" s="13"/>
       <c r="G323" s="13"/>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="13" t="s">
         <v>727</v>
       </c>
@@ -10392,7 +10399,7 @@
       <c r="F324" s="13"/>
       <c r="G324" s="13"/>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="13" t="s">
         <v>730</v>
       </c>
@@ -10409,7 +10416,7 @@
       <c r="F325" s="13"/>
       <c r="G325" s="13"/>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="13" t="s">
         <v>732</v>
       </c>
@@ -10426,7 +10433,7 @@
       <c r="F326" s="13"/>
       <c r="G326" s="13"/>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="13" t="s">
         <v>734</v>
       </c>
@@ -10443,7 +10450,7 @@
       <c r="F327" s="13"/>
       <c r="G327" s="13"/>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="13" t="s">
         <v>736</v>
       </c>
@@ -10460,7 +10467,7 @@
       <c r="F328" s="13"/>
       <c r="G328" s="13"/>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="13" t="s">
         <v>738</v>
       </c>
@@ -10477,7 +10484,7 @@
       <c r="F329" s="13"/>
       <c r="G329" s="13"/>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="13" t="s">
         <v>740</v>
       </c>
@@ -10494,7 +10501,7 @@
       <c r="F330" s="13"/>
       <c r="G330" s="13"/>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="13" t="s">
         <v>743</v>
       </c>
@@ -10511,7 +10518,7 @@
       <c r="F331" s="13"/>
       <c r="G331" s="13"/>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="13" t="s">
         <v>745</v>
       </c>
@@ -10528,7 +10535,7 @@
       <c r="F332" s="13"/>
       <c r="G332" s="13"/>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="13" t="s">
         <v>747</v>
       </c>
@@ -10545,7 +10552,7 @@
       <c r="F333" s="13"/>
       <c r="G333" s="13"/>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="13" t="s">
         <v>750</v>
       </c>
@@ -10562,7 +10569,7 @@
       <c r="F334" s="13"/>
       <c r="G334" s="13"/>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="13" t="s">
         <v>752</v>
       </c>
@@ -10579,7 +10586,7 @@
       <c r="F335" s="13"/>
       <c r="G335" s="13"/>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="13" t="s">
         <v>754</v>
       </c>
@@ -10596,7 +10603,7 @@
       <c r="F336" s="13"/>
       <c r="G336" s="13"/>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="13" t="s">
         <v>756</v>
       </c>
@@ -10613,7 +10620,7 @@
       <c r="F337" s="13"/>
       <c r="G337" s="13"/>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="13" t="s">
         <v>758</v>
       </c>
@@ -10630,7 +10637,7 @@
       <c r="F338" s="13"/>
       <c r="G338" s="13"/>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="13" t="s">
         <v>760</v>
       </c>
@@ -10647,7 +10654,7 @@
       <c r="F339" s="13"/>
       <c r="G339" s="13"/>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="13" t="s">
         <v>762</v>
       </c>
@@ -10664,7 +10671,7 @@
       <c r="F340" s="13"/>
       <c r="G340" s="13"/>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="13" t="s">
         <v>764</v>
       </c>
@@ -10681,7 +10688,7 @@
       <c r="F341" s="13"/>
       <c r="G341" s="13"/>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="13" t="s">
         <v>766</v>
       </c>
@@ -10698,7 +10705,7 @@
       <c r="F342" s="13"/>
       <c r="G342" s="13"/>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="13" t="s">
         <v>769</v>
       </c>
@@ -10715,7 +10722,7 @@
       <c r="F343" s="13"/>
       <c r="G343" s="13"/>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="13" t="s">
         <v>772</v>
       </c>
@@ -10732,7 +10739,7 @@
       <c r="F344" s="13"/>
       <c r="G344" s="13"/>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="13" t="s">
         <v>774</v>
       </c>
@@ -10749,7 +10756,7 @@
       <c r="F345" s="13"/>
       <c r="G345" s="13"/>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="13" t="s">
         <v>776</v>
       </c>
@@ -10766,7 +10773,7 @@
       <c r="F346" s="13"/>
       <c r="G346" s="13"/>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="13" t="s">
         <v>778</v>
       </c>
@@ -10783,7 +10790,7 @@
       <c r="F347" s="13"/>
       <c r="G347" s="13"/>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="13" t="s">
         <v>780</v>
       </c>
@@ -10800,7 +10807,7 @@
       <c r="F348" s="13"/>
       <c r="G348" s="13"/>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="13" t="s">
         <v>782</v>
       </c>
@@ -10817,7 +10824,7 @@
       <c r="F349" s="13"/>
       <c r="G349" s="13"/>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="13" t="s">
         <v>785</v>
       </c>
@@ -10834,7 +10841,7 @@
       <c r="F350" s="13"/>
       <c r="G350" s="13"/>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="13" t="s">
         <v>787</v>
       </c>
@@ -10851,7 +10858,7 @@
       <c r="F351" s="13"/>
       <c r="G351" s="13"/>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="13" t="s">
         <v>789</v>
       </c>
@@ -10892,7 +10899,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="13" t="s">
         <v>793</v>
       </c>
@@ -10909,7 +10916,7 @@
       <c r="F354" s="13"/>
       <c r="G354" s="13"/>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="11" t="s">
         <v>796</v>
       </c>
@@ -10928,7 +10935,7 @@
       <c r="F355" s="13"/>
       <c r="G355" s="13"/>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="11" t="s">
         <v>798</v>
       </c>
@@ -10945,7 +10952,7 @@
       <c r="F356" s="13"/>
       <c r="G356" s="13"/>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="11" t="s">
         <v>800</v>
       </c>
@@ -10962,7 +10969,7 @@
       <c r="F357" s="13"/>
       <c r="G357" s="13"/>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="11" t="s">
         <v>802</v>
       </c>
@@ -11005,7 +11012,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="13" t="s">
         <v>807</v>
       </c>
@@ -11022,7 +11029,7 @@
       <c r="F360" s="13"/>
       <c r="G360" s="13"/>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="13" t="s">
         <v>809</v>
       </c>
@@ -11039,7 +11046,7 @@
       <c r="F361" s="13"/>
       <c r="G361" s="13"/>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="13" t="s">
         <v>812</v>
       </c>
@@ -11056,7 +11063,7 @@
       <c r="F362" s="13"/>
       <c r="G362" s="13"/>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="13" t="s">
         <v>814</v>
       </c>
@@ -11073,7 +11080,7 @@
       <c r="F363" s="13"/>
       <c r="G363" s="13"/>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="13" t="s">
         <v>816</v>
       </c>
@@ -11090,7 +11097,7 @@
       <c r="F364" s="13"/>
       <c r="G364" s="13"/>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="13" t="s">
         <v>818</v>
       </c>
@@ -11107,7 +11114,7 @@
       <c r="F365" s="13"/>
       <c r="G365" s="13"/>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="13" t="s">
         <v>820</v>
       </c>
@@ -11124,7 +11131,7 @@
       <c r="F366" s="13"/>
       <c r="G366" s="13"/>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="13" t="s">
         <v>822</v>
       </c>
@@ -11141,7 +11148,7 @@
       <c r="F367" s="13"/>
       <c r="G367" s="13"/>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="13" t="s">
         <v>824</v>
       </c>
@@ -11158,7 +11165,7 @@
       <c r="F368" s="13"/>
       <c r="G368" s="13"/>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="13" t="s">
         <v>826</v>
       </c>
@@ -11175,7 +11182,7 @@
       <c r="F369" s="13"/>
       <c r="G369" s="13"/>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="13" t="s">
         <v>828</v>
       </c>
@@ -11192,7 +11199,7 @@
       <c r="F370" s="13"/>
       <c r="G370" s="13"/>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="13" t="s">
         <v>831</v>
       </c>
@@ -11211,7 +11218,7 @@
       </c>
       <c r="G371" s="13"/>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="13" t="s">
         <v>833</v>
       </c>
@@ -11228,7 +11235,7 @@
       <c r="F372" s="13"/>
       <c r="G372" s="13"/>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="13" t="s">
         <v>835</v>
       </c>
@@ -11245,7 +11252,7 @@
       <c r="F373" s="13"/>
       <c r="G373" s="13"/>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="13" t="s">
         <v>837</v>
       </c>
@@ -11262,7 +11269,7 @@
       <c r="F374" s="13"/>
       <c r="G374" s="13"/>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="13" t="s">
         <v>839</v>
       </c>
@@ -11279,7 +11286,7 @@
       <c r="F375" s="13"/>
       <c r="G375" s="13"/>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="13" t="s">
         <v>841</v>
       </c>
@@ -11296,7 +11303,7 @@
       <c r="F376" s="13"/>
       <c r="G376" s="13"/>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="13" t="s">
         <v>843</v>
       </c>
@@ -11313,7 +11320,7 @@
       <c r="F377" s="13"/>
       <c r="G377" s="13"/>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="13" t="s">
         <v>845</v>
       </c>
@@ -11330,7 +11337,7 @@
       <c r="F378" s="13"/>
       <c r="G378" s="13"/>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="13" t="s">
         <v>847</v>
       </c>
@@ -11371,7 +11378,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="13" t="s">
         <v>852</v>
       </c>
@@ -11388,7 +11395,7 @@
       <c r="F381" s="13"/>
       <c r="G381" s="13"/>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="13" t="s">
         <v>854</v>
       </c>
@@ -11405,7 +11412,7 @@
       <c r="F382" s="13"/>
       <c r="G382" s="13"/>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="13" t="s">
         <v>857</v>
       </c>
@@ -11422,7 +11429,7 @@
       <c r="F383" s="13"/>
       <c r="G383" s="13"/>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="13" t="s">
         <v>859</v>
       </c>
@@ -11439,7 +11446,7 @@
       <c r="F384" s="13"/>
       <c r="G384" s="13"/>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="13" t="s">
         <v>861</v>
       </c>
@@ -11504,7 +11511,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="13" t="s">
         <v>869</v>
       </c>
@@ -11521,7 +11528,7 @@
       <c r="F388" s="13"/>
       <c r="G388" s="13"/>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="13" t="s">
         <v>872</v>
       </c>
@@ -11538,7 +11545,7 @@
       <c r="F389" s="13"/>
       <c r="G389" s="13"/>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="13" t="s">
         <v>874</v>
       </c>
@@ -11555,7 +11562,7 @@
       <c r="F390" s="13"/>
       <c r="G390" s="13"/>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="13" t="s">
         <v>876</v>
       </c>
@@ -11596,7 +11603,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="13" t="s">
         <v>881</v>
       </c>
@@ -11637,7 +11644,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="13" t="s">
         <v>887</v>
       </c>
@@ -11654,7 +11661,7 @@
       <c r="F395" s="13"/>
       <c r="G395" s="13"/>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6" t="s">
         <v>889</v>
       </c>
@@ -11673,7 +11680,7 @@
       <c r="F396" s="13"/>
       <c r="G396" s="13"/>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="13" t="s">
         <v>891</v>
       </c>
@@ -11690,7 +11697,7 @@
       <c r="F397" s="13"/>
       <c r="G397" s="13"/>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="13" t="s">
         <v>893</v>
       </c>
@@ -11707,7 +11714,7 @@
       <c r="F398" s="13"/>
       <c r="G398" s="13"/>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="13" t="s">
         <v>895</v>
       </c>
@@ -11745,7 +11752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="13" t="s">
         <v>900</v>
       </c>
@@ -11762,7 +11769,7 @@
       <c r="F401" s="13"/>
       <c r="G401" s="13"/>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="13" t="s">
         <v>902</v>
       </c>
@@ -11779,7 +11786,7 @@
       <c r="F402" s="13"/>
       <c r="G402" s="13"/>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="13" t="s">
         <v>904</v>
       </c>
@@ -11796,7 +11803,7 @@
       <c r="F403" s="13"/>
       <c r="G403" s="13"/>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="13" t="s">
         <v>907</v>
       </c>
@@ -11813,7 +11820,7 @@
       <c r="F404" s="13"/>
       <c r="G404" s="13"/>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="13" t="s">
         <v>909</v>
       </c>
@@ -11830,7 +11837,7 @@
       <c r="F405" s="13"/>
       <c r="G405" s="13"/>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="13" t="s">
         <v>911</v>
       </c>
@@ -11847,7 +11854,7 @@
       <c r="F406" s="13"/>
       <c r="G406" s="13"/>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="13" t="s">
         <v>914</v>
       </c>
@@ -11888,7 +11895,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="13" t="s">
         <v>919</v>
       </c>
@@ -11905,7 +11912,7 @@
       <c r="F409" s="13"/>
       <c r="G409" s="13"/>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="13" t="s">
         <v>921</v>
       </c>
@@ -11922,7 +11929,7 @@
       <c r="F410" s="13"/>
       <c r="G410" s="13"/>
     </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="13" t="s">
         <v>924</v>
       </c>
@@ -11939,7 +11946,7 @@
       <c r="F411" s="13"/>
       <c r="G411" s="13"/>
     </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="13" t="s">
         <v>927</v>
       </c>
@@ -11956,7 +11963,7 @@
       <c r="F412" s="13"/>
       <c r="G412" s="13"/>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="13" t="s">
         <v>929</v>
       </c>
@@ -11973,7 +11980,7 @@
       <c r="F413" s="13"/>
       <c r="G413" s="13"/>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="13" t="s">
         <v>931</v>
       </c>
@@ -11990,7 +11997,7 @@
       <c r="F414" s="13"/>
       <c r="G414" s="13"/>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="13" t="s">
         <v>933</v>
       </c>
@@ -12007,7 +12014,7 @@
       <c r="F415" s="13"/>
       <c r="G415" s="13"/>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="13" t="s">
         <v>935</v>
       </c>
@@ -12024,7 +12031,7 @@
       <c r="F416" s="13"/>
       <c r="G416" s="13"/>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="13" t="s">
         <v>938</v>
       </c>
@@ -12041,7 +12048,7 @@
       <c r="F417" s="13"/>
       <c r="G417" s="13"/>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="10" t="s">
         <v>940</v>
       </c>
@@ -12058,7 +12065,7 @@
       <c r="F418" s="13"/>
       <c r="G418" s="13"/>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="13" t="s">
         <v>942</v>
       </c>
@@ -12075,7 +12082,7 @@
       <c r="F419" s="13"/>
       <c r="G419" s="13"/>
     </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="13" t="s">
         <v>945</v>
       </c>
@@ -12092,7 +12099,7 @@
       <c r="F420" s="13"/>
       <c r="G420" s="13"/>
     </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="13" t="s">
         <v>948</v>
       </c>
@@ -12109,7 +12116,7 @@
       <c r="F421" s="13"/>
       <c r="G421" s="13"/>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="13" t="s">
         <v>950</v>
       </c>
@@ -12126,7 +12133,7 @@
       <c r="F422" s="13"/>
       <c r="G422" s="13"/>
     </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="13" t="s">
         <v>952</v>
       </c>
@@ -12143,7 +12150,7 @@
       <c r="F423" s="13"/>
       <c r="G423" s="13"/>
     </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="13" t="s">
         <v>954</v>
       </c>
@@ -12160,7 +12167,7 @@
       <c r="F424" s="13"/>
       <c r="G424" s="13"/>
     </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="13" t="s">
         <v>956</v>
       </c>
@@ -12201,7 +12208,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="13" t="s">
         <v>961</v>
       </c>
@@ -12218,7 +12225,7 @@
       <c r="F427" s="13"/>
       <c r="G427" s="13"/>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="13" t="s">
         <v>963</v>
       </c>
@@ -12235,7 +12242,7 @@
       <c r="F428" s="13"/>
       <c r="G428" s="13"/>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="13" t="s">
         <v>965</v>
       </c>
@@ -12252,7 +12259,7 @@
       <c r="F429" s="13"/>
       <c r="G429" s="13"/>
     </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="13" t="s">
         <v>967</v>
       </c>
@@ -12293,7 +12300,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="13" t="s">
         <v>971</v>
       </c>
@@ -12310,7 +12317,7 @@
       <c r="F432" s="13"/>
       <c r="G432" s="13"/>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="13" t="s">
         <v>974</v>
       </c>
@@ -12327,7 +12334,7 @@
       <c r="F433" s="13"/>
       <c r="G433" s="13"/>
     </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="13" t="s">
         <v>976</v>
       </c>
@@ -12344,7 +12351,7 @@
       <c r="F434" s="13"/>
       <c r="G434" s="13"/>
     </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="13" t="s">
         <v>978</v>
       </c>
@@ -12361,7 +12368,7 @@
       <c r="F435" s="13"/>
       <c r="G435" s="13"/>
     </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="13" t="s">
         <v>980</v>
       </c>
@@ -12378,7 +12385,7 @@
       <c r="F436" s="13"/>
       <c r="G436" s="13"/>
     </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="13" t="s">
         <v>982</v>
       </c>
@@ -12395,7 +12402,7 @@
       <c r="F437" s="13"/>
       <c r="G437" s="13"/>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="13" t="s">
         <v>985</v>
       </c>
@@ -12412,7 +12419,7 @@
       <c r="F438" s="13"/>
       <c r="G438" s="13"/>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="13" t="s">
         <v>988</v>
       </c>
@@ -12429,7 +12436,7 @@
       <c r="F439" s="13"/>
       <c r="G439" s="13"/>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="6" t="s">
         <v>990</v>
       </c>
@@ -12472,7 +12479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="13" t="s">
         <v>996</v>
       </c>
@@ -12489,7 +12496,7 @@
       <c r="F442" s="13"/>
       <c r="G442" s="13"/>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="13" t="s">
         <v>999</v>
       </c>
@@ -12506,7 +12513,7 @@
       <c r="F443" s="13"/>
       <c r="G443" s="13"/>
     </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="13" t="s">
         <v>1001</v>
       </c>
@@ -12523,7 +12530,7 @@
       <c r="F444" s="13"/>
       <c r="G444" s="13"/>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="27" t="s">
         <v>1004</v>
       </c>
@@ -12540,7 +12547,7 @@
       <c r="F445" s="13"/>
       <c r="G445" s="13"/>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="13" t="s">
         <v>1006</v>
       </c>
@@ -12557,7 +12564,7 @@
       <c r="F446" s="13"/>
       <c r="G446" s="13"/>
     </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="6" t="s">
         <v>1008</v>
       </c>
@@ -12576,7 +12583,7 @@
       <c r="F447" s="13"/>
       <c r="G447" s="13"/>
     </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="13" t="s">
         <v>1011</v>
       </c>
@@ -12617,7 +12624,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="13" t="s">
         <v>1016</v>
       </c>
@@ -12634,7 +12641,7 @@
       <c r="F450" s="13"/>
       <c r="G450" s="13"/>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="6" t="s">
         <v>1018</v>
       </c>
@@ -12653,7 +12660,7 @@
       <c r="F451" s="13"/>
       <c r="G451" s="13"/>
     </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="13" t="s">
         <v>1021</v>
       </c>
@@ -12670,7 +12677,7 @@
       <c r="F452" s="13"/>
       <c r="G452" s="13"/>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="13" t="s">
         <v>1024</v>
       </c>
@@ -12687,7 +12694,7 @@
       <c r="F453" s="13"/>
       <c r="G453" s="13"/>
     </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="13" t="s">
         <v>1026</v>
       </c>
@@ -12704,7 +12711,7 @@
       <c r="F454" s="13"/>
       <c r="G454" s="13"/>
     </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="13" t="s">
         <v>1028</v>
       </c>
@@ -12721,7 +12728,7 @@
       <c r="F455" s="13"/>
       <c r="G455" s="13"/>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="10" t="s">
         <v>1030</v>
       </c>
@@ -12738,7 +12745,7 @@
       <c r="F456" s="13"/>
       <c r="G456" s="13"/>
     </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="13" t="s">
         <v>1032</v>
       </c>
@@ -12755,7 +12762,7 @@
       <c r="F457" s="13"/>
       <c r="G457" s="13"/>
     </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="13" t="s">
         <v>1035</v>
       </c>
@@ -12772,7 +12779,7 @@
       <c r="F458" s="13"/>
       <c r="G458" s="13"/>
     </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="10" t="s">
         <v>1037</v>
       </c>
@@ -12789,7 +12796,7 @@
       <c r="F459" s="13"/>
       <c r="G459" s="13"/>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="10" t="s">
         <v>1039</v>
       </c>
@@ -12806,7 +12813,7 @@
       <c r="F460" s="13"/>
       <c r="G460" s="13"/>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="13" t="s">
         <v>1041</v>
       </c>
@@ -12823,7 +12830,7 @@
       <c r="F461" s="13"/>
       <c r="G461" s="13"/>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="6" t="s">
         <v>1044</v>
       </c>
@@ -12864,7 +12871,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="13" t="s">
         <v>1048</v>
       </c>
@@ -12881,7 +12888,7 @@
       <c r="F464" s="13"/>
       <c r="G464" s="13"/>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="13" t="s">
         <v>1050</v>
       </c>
@@ -12898,7 +12905,7 @@
       <c r="F465" s="13"/>
       <c r="G465" s="13"/>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="13" t="s">
         <v>1053</v>
       </c>
@@ -12915,7 +12922,7 @@
       <c r="F466" s="13"/>
       <c r="G466" s="13"/>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="13" t="s">
         <v>1056</v>
       </c>
@@ -12932,7 +12939,7 @@
       <c r="F467" s="13"/>
       <c r="G467" s="13"/>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="13" t="s">
         <v>1058</v>
       </c>
@@ -12949,7 +12956,7 @@
       <c r="F468" s="13"/>
       <c r="G468" s="13"/>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="13" t="s">
         <v>1060</v>
       </c>
@@ -12966,7 +12973,7 @@
       <c r="F469" s="13"/>
       <c r="G469" s="13"/>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="6" t="s">
         <v>1062</v>
       </c>
@@ -12985,7 +12992,7 @@
       </c>
       <c r="G470" s="13"/>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="13" t="s">
         <v>1064</v>
       </c>
@@ -13002,7 +13009,7 @@
       <c r="F471" s="13"/>
       <c r="G471" s="13"/>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="13" t="s">
         <v>1066</v>
       </c>
@@ -13019,7 +13026,7 @@
       <c r="F472" s="13"/>
       <c r="G472" s="13"/>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="13" t="s">
         <v>1069</v>
       </c>
@@ -13036,7 +13043,7 @@
       <c r="F473" s="13"/>
       <c r="G473" s="13"/>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="13" t="s">
         <v>1071</v>
       </c>
@@ -13053,7 +13060,7 @@
       <c r="F474" s="13"/>
       <c r="G474" s="13"/>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="13" t="s">
         <v>1074</v>
       </c>
@@ -13070,7 +13077,7 @@
       <c r="F475" s="13"/>
       <c r="G475" s="13"/>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="13" t="s">
         <v>1076</v>
       </c>
@@ -13087,7 +13094,7 @@
       <c r="F476" s="13"/>
       <c r="G476" s="13"/>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="13" t="s">
         <v>1078</v>
       </c>
@@ -13104,7 +13111,7 @@
       <c r="F477" s="13"/>
       <c r="G477" s="13"/>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="13" t="s">
         <v>1081</v>
       </c>
@@ -13121,7 +13128,7 @@
       <c r="F478" s="13"/>
       <c r="G478" s="13"/>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="13" t="s">
         <v>1084</v>
       </c>
@@ -13138,7 +13145,7 @@
       <c r="F479" s="13"/>
       <c r="G479" s="13"/>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="13" t="s">
         <v>1086</v>
       </c>
@@ -13155,7 +13162,7 @@
       <c r="F480" s="13"/>
       <c r="G480" s="13"/>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="13" t="s">
         <v>1088</v>
       </c>
@@ -13172,7 +13179,7 @@
       <c r="F481" s="13"/>
       <c r="G481" s="13"/>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="13" t="s">
         <v>1091</v>
       </c>
@@ -13189,7 +13196,7 @@
       <c r="F482" s="13"/>
       <c r="G482" s="13"/>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="13" t="s">
         <v>1093</v>
       </c>
@@ -13206,7 +13213,7 @@
       <c r="F483" s="13"/>
       <c r="G483" s="13"/>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="13" t="s">
         <v>1095</v>
       </c>
@@ -13223,7 +13230,7 @@
       <c r="F484" s="13"/>
       <c r="G484" s="13"/>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="13" t="s">
         <v>1097</v>
       </c>
@@ -13240,7 +13247,7 @@
       <c r="F485" s="13"/>
       <c r="G485" s="13"/>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="13" t="s">
         <v>1100</v>
       </c>
@@ -13257,7 +13264,7 @@
       <c r="F486" s="13"/>
       <c r="G486" s="13"/>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="13" t="s">
         <v>1102</v>
       </c>
@@ -13274,7 +13281,7 @@
       <c r="F487" s="13"/>
       <c r="G487" s="13"/>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="13" t="s">
         <v>1105</v>
       </c>
@@ -13291,7 +13298,7 @@
       <c r="F488" s="13"/>
       <c r="G488" s="13"/>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="13" t="s">
         <v>1108</v>
       </c>
@@ -13308,7 +13315,7 @@
       <c r="F489" s="13"/>
       <c r="G489" s="13"/>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="13" t="s">
         <v>1110</v>
       </c>
@@ -13325,7 +13332,7 @@
       <c r="F490" s="13"/>
       <c r="G490" s="13"/>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="13" t="s">
         <v>1112</v>
       </c>
@@ -13342,7 +13349,7 @@
       <c r="F491" s="13"/>
       <c r="G491" s="13"/>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="13" t="s">
         <v>1114</v>
       </c>
@@ -13359,7 +13366,7 @@
       <c r="F492" s="13"/>
       <c r="G492" s="13"/>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="13" t="s">
         <v>1116</v>
       </c>
@@ -13376,7 +13383,7 @@
       <c r="F493" s="13"/>
       <c r="G493" s="13"/>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" s="13" t="s">
         <v>1118</v>
       </c>
@@ -13393,7 +13400,7 @@
       <c r="F494" s="13"/>
       <c r="G494" s="13"/>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" s="13" t="s">
         <v>1120</v>
       </c>
@@ -13410,7 +13417,7 @@
       <c r="F495" s="13"/>
       <c r="G495" s="13"/>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" s="13" t="s">
         <v>1122</v>
       </c>
@@ -13451,7 +13458,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="13" t="s">
         <v>1126</v>
       </c>
@@ -13468,7 +13475,7 @@
       <c r="F498" s="13"/>
       <c r="G498" s="13"/>
     </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="13" t="s">
         <v>1128</v>
       </c>
@@ -13509,7 +13516,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="13" t="s">
         <v>1133</v>
       </c>
@@ -13526,7 +13533,7 @@
       <c r="F501" s="13"/>
       <c r="G501" s="13"/>
     </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="13" t="s">
         <v>1135</v>
       </c>
@@ -13567,7 +13574,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="13" t="s">
         <v>1139</v>
       </c>
@@ -13584,7 +13591,7 @@
       <c r="F504" s="13"/>
       <c r="G504" s="13"/>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="13" t="s">
         <v>1142</v>
       </c>
@@ -13601,7 +13608,7 @@
       <c r="F505" s="13"/>
       <c r="G505" s="13"/>
     </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="6" t="s">
         <v>1144</v>
       </c>
@@ -13620,7 +13627,7 @@
       <c r="F506" s="13"/>
       <c r="G506" s="13"/>
     </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="24" t="s">
         <v>1146</v>
       </c>
@@ -13639,7 +13646,7 @@
       <c r="F507" s="13"/>
       <c r="G507" s="13"/>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="13" t="s">
         <v>1148</v>
       </c>
@@ -13656,7 +13663,7 @@
       <c r="F508" s="13"/>
       <c r="G508" s="13"/>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="13" t="s">
         <v>1150</v>
       </c>
@@ -13673,7 +13680,7 @@
       <c r="F509" s="13"/>
       <c r="G509" s="13"/>
     </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="13" t="s">
         <v>1152</v>
       </c>
@@ -13690,7 +13697,7 @@
       <c r="F510" s="13"/>
       <c r="G510" s="13"/>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="10" t="s">
         <v>1155</v>
       </c>
@@ -13707,7 +13714,7 @@
       <c r="F511" s="13"/>
       <c r="G511" s="13"/>
     </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="13" t="s">
         <v>1157</v>
       </c>
@@ -13724,7 +13731,7 @@
       <c r="F512" s="13"/>
       <c r="G512" s="13"/>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="13" t="s">
         <v>1159</v>
       </c>
@@ -13741,7 +13748,7 @@
       <c r="F513" s="13"/>
       <c r="G513" s="13"/>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="6" t="s">
         <v>1161</v>
       </c>
@@ -13760,7 +13767,7 @@
       <c r="F514" s="13"/>
       <c r="G514" s="13"/>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="13" t="s">
         <v>1163</v>
       </c>
@@ -13777,7 +13784,7 @@
       <c r="F515" s="13"/>
       <c r="G515" s="13"/>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="13" t="s">
         <v>1165</v>
       </c>
@@ -13794,7 +13801,7 @@
       <c r="F516" s="13"/>
       <c r="G516" s="13"/>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="13" t="s">
         <v>1167</v>
       </c>
@@ -13811,7 +13818,7 @@
       <c r="F517" s="13"/>
       <c r="G517" s="13"/>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="13" t="s">
         <v>1169</v>
       </c>
@@ -13828,7 +13835,7 @@
       <c r="F518" s="13"/>
       <c r="G518" s="13"/>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="13" t="s">
         <v>1171</v>
       </c>
@@ -13845,7 +13852,7 @@
       <c r="F519" s="13"/>
       <c r="G519" s="13"/>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="29" t="s">
         <v>1173</v>
       </c>
@@ -13864,7 +13871,7 @@
       <c r="F520" s="13"/>
       <c r="G520" s="13"/>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="13" t="s">
         <v>1175</v>
       </c>
@@ -13881,7 +13888,7 @@
       <c r="F521" s="13"/>
       <c r="G521" s="13"/>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="13" t="s">
         <v>1178</v>
       </c>
@@ -13898,7 +13905,7 @@
       <c r="F522" s="13"/>
       <c r="G522" s="13"/>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="13" t="s">
         <v>1180</v>
       </c>
@@ -13915,7 +13922,7 @@
       <c r="F523" s="13"/>
       <c r="G523" s="13"/>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="6" t="s">
         <v>1183</v>
       </c>
@@ -13934,7 +13941,7 @@
       <c r="F524" s="13"/>
       <c r="G524" s="13"/>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="13" t="s">
         <v>1185</v>
       </c>
@@ -13951,7 +13958,7 @@
       <c r="F525" s="13"/>
       <c r="G525" s="13"/>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="13" t="s">
         <v>1187</v>
       </c>
@@ -13968,7 +13975,7 @@
       <c r="F526" s="13"/>
       <c r="G526" s="13"/>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="13" t="s">
         <v>1190</v>
       </c>
@@ -13985,7 +13992,7 @@
       <c r="F527" s="13"/>
       <c r="G527" s="13"/>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="13" t="s">
         <v>1193</v>
       </c>
@@ -14002,7 +14009,7 @@
       <c r="F528" s="13"/>
       <c r="G528" s="13"/>
     </row>
-    <row r="529" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="13" t="s">
         <v>1195</v>
       </c>
@@ -14019,7 +14026,7 @@
       <c r="F529" s="13"/>
       <c r="G529" s="13"/>
     </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="13" t="s">
         <v>1197</v>
       </c>
@@ -14036,7 +14043,7 @@
       <c r="F530" s="13"/>
       <c r="G530" s="13"/>
     </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="10" t="s">
         <v>1199</v>
       </c>
@@ -14055,7 +14062,7 @@
       </c>
       <c r="G531" s="13"/>
     </row>
-    <row r="532" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="13" t="s">
         <v>1202</v>
       </c>
@@ -14072,7 +14079,7 @@
       <c r="F532" s="13"/>
       <c r="G532" s="13"/>
     </row>
-    <row r="533" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="13" t="s">
         <v>1204</v>
       </c>
@@ -14089,7 +14096,7 @@
       <c r="F533" s="13"/>
       <c r="G533" s="13"/>
     </row>
-    <row r="534" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="13" t="s">
         <v>1206</v>
       </c>
@@ -14130,7 +14137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="13" t="s">
         <v>1210</v>
       </c>
@@ -14147,7 +14154,7 @@
       <c r="F536" s="13"/>
       <c r="G536" s="13"/>
     </row>
-    <row r="537" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="13" t="s">
         <v>1212</v>
       </c>
@@ -14164,7 +14171,7 @@
       <c r="F537" s="13"/>
       <c r="G537" s="13"/>
     </row>
-    <row r="538" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="13" t="s">
         <v>1214</v>
       </c>
@@ -14181,7 +14188,7 @@
       <c r="F538" s="13"/>
       <c r="G538" s="13"/>
     </row>
-    <row r="539" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="13" t="s">
         <v>1216</v>
       </c>
@@ -14198,7 +14205,7 @@
       <c r="F539" s="13"/>
       <c r="G539" s="13"/>
     </row>
-    <row r="540" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="13" t="s">
         <v>1218</v>
       </c>
@@ -14215,7 +14222,7 @@
       <c r="F540" s="13"/>
       <c r="G540" s="13"/>
     </row>
-    <row r="541" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="13" t="s">
         <v>1220</v>
       </c>
@@ -14232,7 +14239,7 @@
       <c r="F541" s="13"/>
       <c r="G541" s="13"/>
     </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="13" t="s">
         <v>1222</v>
       </c>
@@ -14249,7 +14256,7 @@
       <c r="F542" s="13"/>
       <c r="G542" s="13"/>
     </row>
-    <row r="543" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="13" t="s">
         <v>1224</v>
       </c>
@@ -14266,7 +14273,7 @@
       <c r="F543" s="13"/>
       <c r="G543" s="13"/>
     </row>
-    <row r="544" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="13" t="s">
         <v>1226</v>
       </c>
@@ -14283,7 +14290,7 @@
       <c r="F544" s="13"/>
       <c r="G544" s="13"/>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="13" t="s">
         <v>1228</v>
       </c>
@@ -14300,7 +14307,7 @@
       <c r="F545" s="13"/>
       <c r="G545" s="13"/>
     </row>
-    <row r="546" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="13" t="s">
         <v>1231</v>
       </c>
@@ -14317,7 +14324,7 @@
       <c r="F546" s="13"/>
       <c r="G546" s="13"/>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="13" t="s">
         <v>1233</v>
       </c>
@@ -14334,7 +14341,7 @@
       <c r="F547" s="13"/>
       <c r="G547" s="13"/>
     </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="13" t="s">
         <v>1235</v>
       </c>
@@ -14351,7 +14358,7 @@
       <c r="F548" s="13"/>
       <c r="G548" s="13"/>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="13" t="s">
         <v>1237</v>
       </c>
@@ -14368,7 +14375,7 @@
       <c r="F549" s="13"/>
       <c r="G549" s="13"/>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="13" t="s">
         <v>1239</v>
       </c>
@@ -14385,7 +14392,7 @@
       <c r="F550" s="13"/>
       <c r="G550" s="13"/>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="13" t="s">
         <v>1241</v>
       </c>
@@ -14402,7 +14409,7 @@
       <c r="F551" s="13"/>
       <c r="G551" s="13"/>
     </row>
-    <row r="552" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="13" t="s">
         <v>1243</v>
       </c>
@@ -14419,7 +14426,7 @@
       <c r="F552" s="13"/>
       <c r="G552" s="13"/>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="13" t="s">
         <v>1245</v>
       </c>
@@ -14436,7 +14443,7 @@
       <c r="F553" s="13"/>
       <c r="G553" s="13"/>
     </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="13" t="s">
         <v>1248</v>
       </c>
@@ -14477,7 +14484,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="13" t="s">
         <v>1252</v>
       </c>
@@ -14494,7 +14501,7 @@
       <c r="F556" s="13"/>
       <c r="G556" s="13"/>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="13" t="s">
         <v>1255</v>
       </c>
@@ -14511,7 +14518,7 @@
       <c r="F557" s="13"/>
       <c r="G557" s="13"/>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="13" t="s">
         <v>1257</v>
       </c>
@@ -14528,7 +14535,7 @@
       <c r="F558" s="13"/>
       <c r="G558" s="13"/>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="13" t="s">
         <v>1259</v>
       </c>
@@ -14545,7 +14552,7 @@
       <c r="F559" s="13"/>
       <c r="G559" s="13"/>
     </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="13" t="s">
         <v>1261</v>
       </c>
@@ -14562,7 +14569,7 @@
       <c r="F560" s="13"/>
       <c r="G560" s="13"/>
     </row>
-    <row r="561" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="13" t="s">
         <v>1263</v>
       </c>
@@ -14579,7 +14586,7 @@
       <c r="F561" s="13"/>
       <c r="G561" s="13"/>
     </row>
-    <row r="562" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="13" t="s">
         <v>1265</v>
       </c>
@@ -14598,7 +14605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="13" t="s">
         <v>1267</v>
       </c>
@@ -14615,7 +14622,7 @@
       <c r="F563" s="13"/>
       <c r="G563" s="13"/>
     </row>
-    <row r="564" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="13" t="s">
         <v>1269</v>
       </c>
@@ -14632,7 +14639,7 @@
       <c r="F564" s="13"/>
       <c r="G564" s="13"/>
     </row>
-    <row r="565" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="13" t="s">
         <v>1271</v>
       </c>
@@ -14649,7 +14656,7 @@
       <c r="F565" s="13"/>
       <c r="G565" s="13"/>
     </row>
-    <row r="566" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="13" t="s">
         <v>1273</v>
       </c>
@@ -14666,7 +14673,7 @@
       <c r="F566" s="13"/>
       <c r="G566" s="13"/>
     </row>
-    <row r="567" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="13" t="s">
         <v>1275</v>
       </c>
@@ -14707,7 +14714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="569" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="13" t="s">
         <v>1279</v>
       </c>
@@ -14724,7 +14731,7 @@
       <c r="F569" s="13"/>
       <c r="G569" s="13"/>
     </row>
-    <row r="570" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="13" t="s">
         <v>1282</v>
       </c>
@@ -14741,7 +14748,7 @@
       <c r="F570" s="13"/>
       <c r="G570" s="13"/>
     </row>
-    <row r="571" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="13" t="s">
         <v>1285</v>
       </c>
@@ -14758,7 +14765,7 @@
       <c r="F571" s="13"/>
       <c r="G571" s="13"/>
     </row>
-    <row r="572" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="13" t="s">
         <v>1287</v>
       </c>
@@ -14775,7 +14782,7 @@
       <c r="F572" s="13"/>
       <c r="G572" s="13"/>
     </row>
-    <row r="573" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="13" t="s">
         <v>1289</v>
       </c>
@@ -14792,7 +14799,7 @@
       <c r="F573" s="13"/>
       <c r="G573" s="13"/>
     </row>
-    <row r="574" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="13" t="s">
         <v>1291</v>
       </c>
@@ -14809,7 +14816,7 @@
       <c r="F574" s="13"/>
       <c r="G574" s="13"/>
     </row>
-    <row r="575" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="13" t="s">
         <v>1293</v>
       </c>
@@ -14826,7 +14833,7 @@
       <c r="F575" s="13"/>
       <c r="G575" s="13"/>
     </row>
-    <row r="576" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="13" t="s">
         <v>1295</v>
       </c>
@@ -14843,7 +14850,7 @@
       <c r="F576" s="13"/>
       <c r="G576" s="13"/>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="13" t="s">
         <v>1297</v>
       </c>
@@ -14860,7 +14867,7 @@
       <c r="F577" s="13"/>
       <c r="G577" s="13"/>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="13" t="s">
         <v>1299</v>
       </c>
@@ -14877,7 +14884,7 @@
       <c r="F578" s="13"/>
       <c r="G578" s="13"/>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" s="13" t="s">
         <v>1301</v>
       </c>
@@ -14894,7 +14901,7 @@
       <c r="F579" s="13"/>
       <c r="G579" s="13"/>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="13" t="s">
         <v>1303</v>
       </c>
@@ -14911,7 +14918,7 @@
       <c r="F580" s="13"/>
       <c r="G580" s="13"/>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="13" t="s">
         <v>1305</v>
       </c>
@@ -14928,7 +14935,7 @@
       <c r="F581" s="13"/>
       <c r="G581" s="13"/>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" s="13" t="s">
         <v>1307</v>
       </c>
@@ -14945,7 +14952,7 @@
       <c r="F582" s="13"/>
       <c r="G582" s="13"/>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="13" t="s">
         <v>1309</v>
       </c>
@@ -14962,7 +14969,7 @@
       <c r="F583" s="13"/>
       <c r="G583" s="13"/>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="13" t="s">
         <v>1311</v>
       </c>
@@ -14979,7 +14986,7 @@
       <c r="F584" s="13"/>
       <c r="G584" s="13"/>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="13" t="s">
         <v>1313</v>
       </c>
@@ -14996,7 +15003,7 @@
       <c r="F585" s="13"/>
       <c r="G585" s="13"/>
     </row>
-    <row r="586" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="13" t="s">
         <v>1315</v>
       </c>
@@ -15013,7 +15020,7 @@
       <c r="F586" s="13"/>
       <c r="G586" s="13"/>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="13" t="s">
         <v>1317</v>
       </c>
@@ -15030,7 +15037,7 @@
       <c r="F587" s="13"/>
       <c r="G587" s="13"/>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="13" t="s">
         <v>1319</v>
       </c>
@@ -15047,7 +15054,7 @@
       <c r="F588" s="13"/>
       <c r="G588" s="13"/>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" s="13" t="s">
         <v>1321</v>
       </c>
@@ -15064,7 +15071,7 @@
       <c r="F589" s="13"/>
       <c r="G589" s="13"/>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="13" t="s">
         <v>1323</v>
       </c>
@@ -15081,7 +15088,7 @@
       <c r="F590" s="13"/>
       <c r="G590" s="13"/>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="13" t="s">
         <v>1325</v>
       </c>
@@ -15098,7 +15105,7 @@
       <c r="F591" s="13"/>
       <c r="G591" s="13"/>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" s="13" t="s">
         <v>1327</v>
       </c>
@@ -15115,7 +15122,7 @@
       <c r="F592" s="13"/>
       <c r="G592" s="13"/>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="13" t="s">
         <v>1329</v>
       </c>
@@ -15132,7 +15139,7 @@
       <c r="F593" s="13"/>
       <c r="G593" s="13"/>
     </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="13" t="s">
         <v>1332</v>
       </c>
@@ -15149,7 +15156,7 @@
       <c r="F594" s="13"/>
       <c r="G594" s="13"/>
     </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="13" t="s">
         <v>1334</v>
       </c>
@@ -15166,7 +15173,7 @@
       <c r="F595" s="13"/>
       <c r="G595" s="13"/>
     </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="13" t="s">
         <v>1336</v>
       </c>
@@ -15183,7 +15190,7 @@
       <c r="F596" s="13"/>
       <c r="G596" s="13"/>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="13" t="s">
         <v>1338</v>
       </c>
@@ -15200,7 +15207,7 @@
       <c r="F597" s="13"/>
       <c r="G597" s="13"/>
     </row>
-    <row r="598" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="6" t="s">
         <v>1340</v>
       </c>
@@ -15219,7 +15226,7 @@
       </c>
       <c r="G598" s="13"/>
     </row>
-    <row r="599" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="13" t="s">
         <v>1342</v>
       </c>
@@ -15237,6 +15244,15 @@
       <c r="G599" s="13"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H599">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="1"/>
+        <filter val="2"/>
+        <filter val="3"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="B1">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>

--- a/01. Preprocessing data/data_CSV/06_Tumor.xlsx
+++ b/01. Preprocessing data/data_CSV/06_Tumor.xlsx
@@ -4,17 +4,18 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" codeName="ЭтаКнига" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Descr" sheetId="1" r:id="rId1"/>
-    <sheet name="morphologyStructureTumor" sheetId="2" r:id="rId2"/>
-    <sheet name="Receptors" sheetId="3" r:id="rId3"/>
+    <sheet name="isTumor" sheetId="4" r:id="rId2"/>
+    <sheet name="morphologyStructureTumor" sheetId="2" r:id="rId3"/>
+    <sheet name="Receptors" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Descr!$A$1:$D$599</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">morphologyStructureTumor!$A$1:$C$611</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Receptors!$A$1:$C$600</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">morphologyStructureTumor!$A$1:$C$611</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Receptors!$A$1:$C$600</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3624" uniqueCount="1202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4823" uniqueCount="1204">
   <si>
     <t>ID</t>
   </si>
@@ -3632,13 +3633,19 @@
   </si>
   <si>
     <t>id598</t>
+  </si>
+  <si>
+    <t>isTumor</t>
+  </si>
+  <si>
+    <t>IDPatient</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3667,8 +3674,17 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3717,6 +3733,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -3745,7 +3767,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3769,11 +3791,33 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -10263,16 +10307,6622 @@
   </sheetData>
   <autoFilter ref="A1:D599"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист4"/>
+  <dimension ref="A1:C599"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="11.5546875"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>603</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B2" t="s">
+        <v>604</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>525</v>
+      </c>
+      <c r="B4" t="s">
+        <v>606</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B5" t="s">
+        <v>607</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>608</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B7" t="s">
+        <v>609</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" t="s">
+        <v>610</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>532</v>
+      </c>
+      <c r="B9" t="s">
+        <v>611</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" t="s">
+        <v>612</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>478</v>
+      </c>
+      <c r="B11" t="s">
+        <v>613</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>166</v>
+      </c>
+      <c r="B12" t="s">
+        <v>614</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B13" t="s">
+        <v>615</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>267</v>
+      </c>
+      <c r="B14" t="s">
+        <v>616</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>239</v>
+      </c>
+      <c r="B15" t="s">
+        <v>617</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>366</v>
+      </c>
+      <c r="B16" t="s">
+        <v>618</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s">
+        <v>619</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>353</v>
+      </c>
+      <c r="B18" t="s">
+        <v>620</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>588</v>
+      </c>
+      <c r="B19" t="s">
+        <v>621</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>170</v>
+      </c>
+      <c r="B20" t="s">
+        <v>622</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>539</v>
+      </c>
+      <c r="B21" t="s">
+        <v>623</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" t="s">
+        <v>624</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>175</v>
+      </c>
+      <c r="B23" t="s">
+        <v>625</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>228</v>
+      </c>
+      <c r="B24" t="s">
+        <v>626</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>318</v>
+      </c>
+      <c r="B25" t="s">
+        <v>627</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B26" t="s">
+        <v>628</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>180</v>
+      </c>
+      <c r="B27" t="s">
+        <v>629</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" t="s">
+        <v>630</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>344</v>
+      </c>
+      <c r="B29" t="s">
+        <v>631</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>377</v>
+      </c>
+      <c r="B30" t="s">
+        <v>632</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>374</v>
+      </c>
+      <c r="B31" t="s">
+        <v>633</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>320</v>
+      </c>
+      <c r="B32" t="s">
+        <v>634</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>470</v>
+      </c>
+      <c r="B33" t="s">
+        <v>635</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>499</v>
+      </c>
+      <c r="B34" t="s">
+        <v>636</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>275</v>
+      </c>
+      <c r="B35" t="s">
+        <v>637</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>367</v>
+      </c>
+      <c r="B36" t="s">
+        <v>638</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" t="s">
+        <v>639</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>446</v>
+      </c>
+      <c r="B38" t="s">
+        <v>640</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>163</v>
+      </c>
+      <c r="B39" t="s">
+        <v>641</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>440</v>
+      </c>
+      <c r="B40" t="s">
+        <v>642</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>436</v>
+      </c>
+      <c r="B41" t="s">
+        <v>643</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>274</v>
+      </c>
+      <c r="B42" t="s">
+        <v>644</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>504</v>
+      </c>
+      <c r="B43" t="s">
+        <v>645</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>488</v>
+      </c>
+      <c r="B44" t="s">
+        <v>646</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>568</v>
+      </c>
+      <c r="B45" t="s">
+        <v>647</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>572</v>
+      </c>
+      <c r="B46" t="s">
+        <v>648</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>415</v>
+      </c>
+      <c r="B47" t="s">
+        <v>649</v>
+      </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>571</v>
+      </c>
+      <c r="B48" t="s">
+        <v>650</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>277</v>
+      </c>
+      <c r="B49" t="s">
+        <v>651</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>188</v>
+      </c>
+      <c r="B50" t="s">
+        <v>652</v>
+      </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>375</v>
+      </c>
+      <c r="B51" t="s">
+        <v>653</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>452</v>
+      </c>
+      <c r="B52" t="s">
+        <v>654</v>
+      </c>
+      <c r="C52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>477</v>
+      </c>
+      <c r="B53" t="s">
+        <v>655</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B54" t="s">
+        <v>656</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>419</v>
+      </c>
+      <c r="B55" t="s">
+        <v>657</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>52</v>
+      </c>
+      <c r="B56" t="s">
+        <v>658</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>217</v>
+      </c>
+      <c r="B57" t="s">
+        <v>659</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>129</v>
+      </c>
+      <c r="B58" t="s">
+        <v>660</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>362</v>
+      </c>
+      <c r="B59" t="s">
+        <v>661</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" t="s">
+        <v>662</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>459</v>
+      </c>
+      <c r="B61" t="s">
+        <v>663</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>269</v>
+      </c>
+      <c r="B62" t="s">
+        <v>664</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>327</v>
+      </c>
+      <c r="B63" t="s">
+        <v>665</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>219</v>
+      </c>
+      <c r="B64" t="s">
+        <v>666</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>157</v>
+      </c>
+      <c r="B65" t="s">
+        <v>667</v>
+      </c>
+      <c r="C65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>149</v>
+      </c>
+      <c r="B66" t="s">
+        <v>668</v>
+      </c>
+      <c r="C66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>449</v>
+      </c>
+      <c r="B67" t="s">
+        <v>669</v>
+      </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>134</v>
+      </c>
+      <c r="B68" t="s">
+        <v>670</v>
+      </c>
+      <c r="C68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>515</v>
+      </c>
+      <c r="B69" t="s">
+        <v>671</v>
+      </c>
+      <c r="C69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>75</v>
+      </c>
+      <c r="B70" t="s">
+        <v>672</v>
+      </c>
+      <c r="C70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>254</v>
+      </c>
+      <c r="B71" t="s">
+        <v>673</v>
+      </c>
+      <c r="C71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>194</v>
+      </c>
+      <c r="B72" t="s">
+        <v>674</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>122</v>
+      </c>
+      <c r="B73" t="s">
+        <v>675</v>
+      </c>
+      <c r="C73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>545</v>
+      </c>
+      <c r="B74" t="s">
+        <v>676</v>
+      </c>
+      <c r="C74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>179</v>
+      </c>
+      <c r="B75" t="s">
+        <v>677</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" t="s">
+        <v>678</v>
+      </c>
+      <c r="C76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>120</v>
+      </c>
+      <c r="B77" t="s">
+        <v>679</v>
+      </c>
+      <c r="C77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>433</v>
+      </c>
+      <c r="B78" t="s">
+        <v>680</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>17</v>
+      </c>
+      <c r="B79" t="s">
+        <v>681</v>
+      </c>
+      <c r="C79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>357</v>
+      </c>
+      <c r="B80" t="s">
+        <v>682</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>295</v>
+      </c>
+      <c r="B81" t="s">
+        <v>683</v>
+      </c>
+      <c r="C81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>178</v>
+      </c>
+      <c r="B82" t="s">
+        <v>684</v>
+      </c>
+      <c r="C82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>345</v>
+      </c>
+      <c r="B83" t="s">
+        <v>685</v>
+      </c>
+      <c r="C83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>282</v>
+      </c>
+      <c r="B84" t="s">
+        <v>686</v>
+      </c>
+      <c r="C84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>548</v>
+      </c>
+      <c r="B85" t="s">
+        <v>687</v>
+      </c>
+      <c r="C85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>74</v>
+      </c>
+      <c r="B86" t="s">
+        <v>688</v>
+      </c>
+      <c r="C86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>559</v>
+      </c>
+      <c r="B87" t="s">
+        <v>689</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>168</v>
+      </c>
+      <c r="B88" t="s">
+        <v>690</v>
+      </c>
+      <c r="C88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>531</v>
+      </c>
+      <c r="B89" t="s">
+        <v>691</v>
+      </c>
+      <c r="C89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>278</v>
+      </c>
+      <c r="B90" t="s">
+        <v>692</v>
+      </c>
+      <c r="C90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>480</v>
+      </c>
+      <c r="B91" t="s">
+        <v>693</v>
+      </c>
+      <c r="C91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>441</v>
+      </c>
+      <c r="B92" t="s">
+        <v>694</v>
+      </c>
+      <c r="C92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>337</v>
+      </c>
+      <c r="B93" t="s">
+        <v>695</v>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>181</v>
+      </c>
+      <c r="B94" t="s">
+        <v>696</v>
+      </c>
+      <c r="C94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>570</v>
+      </c>
+      <c r="B95" t="s">
+        <v>697</v>
+      </c>
+      <c r="C95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>231</v>
+      </c>
+      <c r="B96" t="s">
+        <v>698</v>
+      </c>
+      <c r="C96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>288</v>
+      </c>
+      <c r="B97" t="s">
+        <v>699</v>
+      </c>
+      <c r="C97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>200</v>
+      </c>
+      <c r="B98" t="s">
+        <v>700</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>474</v>
+      </c>
+      <c r="B99" t="s">
+        <v>701</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>404</v>
+      </c>
+      <c r="B100" t="s">
+        <v>702</v>
+      </c>
+      <c r="C100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>351</v>
+      </c>
+      <c r="B101" t="s">
+        <v>703</v>
+      </c>
+      <c r="C101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>151</v>
+      </c>
+      <c r="B102" t="s">
+        <v>704</v>
+      </c>
+      <c r="C102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>427</v>
+      </c>
+      <c r="B103" t="s">
+        <v>705</v>
+      </c>
+      <c r="C103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>587</v>
+      </c>
+      <c r="B104" t="s">
+        <v>706</v>
+      </c>
+      <c r="C104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>36</v>
+      </c>
+      <c r="B105" t="s">
+        <v>707</v>
+      </c>
+      <c r="C105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>392</v>
+      </c>
+      <c r="B106" t="s">
+        <v>708</v>
+      </c>
+      <c r="C106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>709</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>420</v>
+      </c>
+      <c r="B108" t="s">
+        <v>710</v>
+      </c>
+      <c r="C108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>66</v>
+      </c>
+      <c r="B109" t="s">
+        <v>711</v>
+      </c>
+      <c r="C109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>413</v>
+      </c>
+      <c r="B110" t="s">
+        <v>712</v>
+      </c>
+      <c r="C110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>445</v>
+      </c>
+      <c r="B111" t="s">
+        <v>713</v>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>421</v>
+      </c>
+      <c r="B112" t="s">
+        <v>714</v>
+      </c>
+      <c r="C112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>195</v>
+      </c>
+      <c r="B113" t="s">
+        <v>715</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>174</v>
+      </c>
+      <c r="B114" t="s">
+        <v>716</v>
+      </c>
+      <c r="C114">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>411</v>
+      </c>
+      <c r="B115" t="s">
+        <v>717</v>
+      </c>
+      <c r="C115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>325</v>
+      </c>
+      <c r="B116" t="s">
+        <v>718</v>
+      </c>
+      <c r="C116">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>29</v>
+      </c>
+      <c r="B117" t="s">
+        <v>719</v>
+      </c>
+      <c r="C117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>567</v>
+      </c>
+      <c r="B118" t="s">
+        <v>720</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>287</v>
+      </c>
+      <c r="B119" t="s">
+        <v>721</v>
+      </c>
+      <c r="C119">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>447</v>
+      </c>
+      <c r="B120" t="s">
+        <v>722</v>
+      </c>
+      <c r="C120">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>505</v>
+      </c>
+      <c r="B121" t="s">
+        <v>723</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>584</v>
+      </c>
+      <c r="B122" t="s">
+        <v>724</v>
+      </c>
+      <c r="C122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>581</v>
+      </c>
+      <c r="B123" t="s">
+        <v>725</v>
+      </c>
+      <c r="C123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>310</v>
+      </c>
+      <c r="B124" t="s">
+        <v>726</v>
+      </c>
+      <c r="C124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>590</v>
+      </c>
+      <c r="B125" t="s">
+        <v>727</v>
+      </c>
+      <c r="C125">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>534</v>
+      </c>
+      <c r="B126" t="s">
+        <v>728</v>
+      </c>
+      <c r="C126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>25</v>
+      </c>
+      <c r="B127" t="s">
+        <v>729</v>
+      </c>
+      <c r="C127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>165</v>
+      </c>
+      <c r="B128" t="s">
+        <v>730</v>
+      </c>
+      <c r="C128">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>199</v>
+      </c>
+      <c r="B129" t="s">
+        <v>731</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>210</v>
+      </c>
+      <c r="B130" t="s">
+        <v>732</v>
+      </c>
+      <c r="C130">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>486</v>
+      </c>
+      <c r="B131" t="s">
+        <v>733</v>
+      </c>
+      <c r="C131">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>300</v>
+      </c>
+      <c r="B132" t="s">
+        <v>734</v>
+      </c>
+      <c r="C132">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>481</v>
+      </c>
+      <c r="B133" t="s">
+        <v>735</v>
+      </c>
+      <c r="C133">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>119</v>
+      </c>
+      <c r="B134" t="s">
+        <v>736</v>
+      </c>
+      <c r="C134">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>264</v>
+      </c>
+      <c r="B135" t="s">
+        <v>737</v>
+      </c>
+      <c r="C135">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>340</v>
+      </c>
+      <c r="B136" t="s">
+        <v>738</v>
+      </c>
+      <c r="C136">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>576</v>
+      </c>
+      <c r="B137" t="s">
+        <v>739</v>
+      </c>
+      <c r="C137">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>406</v>
+      </c>
+      <c r="B138" t="s">
+        <v>740</v>
+      </c>
+      <c r="C138">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>355</v>
+      </c>
+      <c r="B139" t="s">
+        <v>741</v>
+      </c>
+      <c r="C139">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>429</v>
+      </c>
+      <c r="B140" t="s">
+        <v>742</v>
+      </c>
+      <c r="C140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>594</v>
+      </c>
+      <c r="B141" t="s">
+        <v>743</v>
+      </c>
+      <c r="C141">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>307</v>
+      </c>
+      <c r="B142" t="s">
+        <v>744</v>
+      </c>
+      <c r="C142">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>16</v>
+      </c>
+      <c r="B143" t="s">
+        <v>745</v>
+      </c>
+      <c r="C143">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>402</v>
+      </c>
+      <c r="B144" t="s">
+        <v>746</v>
+      </c>
+      <c r="C144">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>304</v>
+      </c>
+      <c r="B145" t="s">
+        <v>747</v>
+      </c>
+      <c r="C145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>215</v>
+      </c>
+      <c r="B146" t="s">
+        <v>748</v>
+      </c>
+      <c r="C146">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>176</v>
+      </c>
+      <c r="B147" t="s">
+        <v>749</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>438</v>
+      </c>
+      <c r="B148" t="s">
+        <v>750</v>
+      </c>
+      <c r="C148">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>48</v>
+      </c>
+      <c r="B149" t="s">
+        <v>751</v>
+      </c>
+      <c r="C149">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>235</v>
+      </c>
+      <c r="B150" t="s">
+        <v>752</v>
+      </c>
+      <c r="C150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>431</v>
+      </c>
+      <c r="B151" t="s">
+        <v>753</v>
+      </c>
+      <c r="C151">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>276</v>
+      </c>
+      <c r="B152" t="s">
+        <v>754</v>
+      </c>
+      <c r="C152">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>236</v>
+      </c>
+      <c r="B153" t="s">
+        <v>755</v>
+      </c>
+      <c r="C153">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>110</v>
+      </c>
+      <c r="B154" t="s">
+        <v>756</v>
+      </c>
+      <c r="C154">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>596</v>
+      </c>
+      <c r="B155" t="s">
+        <v>757</v>
+      </c>
+      <c r="C155">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>130</v>
+      </c>
+      <c r="B156" t="s">
+        <v>758</v>
+      </c>
+      <c r="C156">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>270</v>
+      </c>
+      <c r="B157" t="s">
+        <v>759</v>
+      </c>
+      <c r="C157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>9</v>
+      </c>
+      <c r="B158" t="s">
+        <v>760</v>
+      </c>
+      <c r="C158">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>322</v>
+      </c>
+      <c r="B159" t="s">
+        <v>761</v>
+      </c>
+      <c r="C159">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>508</v>
+      </c>
+      <c r="B160" t="s">
+        <v>762</v>
+      </c>
+      <c r="C160">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>511</v>
+      </c>
+      <c r="B161" t="s">
+        <v>763</v>
+      </c>
+      <c r="C161">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>214</v>
+      </c>
+      <c r="B162" t="s">
+        <v>764</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>335</v>
+      </c>
+      <c r="B163" t="s">
+        <v>765</v>
+      </c>
+      <c r="C163">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>289</v>
+      </c>
+      <c r="B164" t="s">
+        <v>766</v>
+      </c>
+      <c r="C164">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>147</v>
+      </c>
+      <c r="B165" t="s">
+        <v>767</v>
+      </c>
+      <c r="C165">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>347</v>
+      </c>
+      <c r="B166" t="s">
+        <v>768</v>
+      </c>
+      <c r="C166">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>155</v>
+      </c>
+      <c r="B167" t="s">
+        <v>769</v>
+      </c>
+      <c r="C167">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>558</v>
+      </c>
+      <c r="B168" t="s">
+        <v>770</v>
+      </c>
+      <c r="C168">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>125</v>
+      </c>
+      <c r="B169" t="s">
+        <v>771</v>
+      </c>
+      <c r="C169">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>378</v>
+      </c>
+      <c r="B170" t="s">
+        <v>772</v>
+      </c>
+      <c r="C170">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>348</v>
+      </c>
+      <c r="B171" t="s">
+        <v>773</v>
+      </c>
+      <c r="C171">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>547</v>
+      </c>
+      <c r="B172" t="s">
+        <v>774</v>
+      </c>
+      <c r="C172">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>167</v>
+      </c>
+      <c r="B173" t="s">
+        <v>775</v>
+      </c>
+      <c r="C173">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>117</v>
+      </c>
+      <c r="B174" t="s">
+        <v>776</v>
+      </c>
+      <c r="C174">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>102</v>
+      </c>
+      <c r="B175" t="s">
+        <v>777</v>
+      </c>
+      <c r="C175">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>434</v>
+      </c>
+      <c r="B176" t="s">
+        <v>778</v>
+      </c>
+      <c r="C176">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>230</v>
+      </c>
+      <c r="B177" t="s">
+        <v>779</v>
+      </c>
+      <c r="C177">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>27</v>
+      </c>
+      <c r="B178" t="s">
+        <v>780</v>
+      </c>
+      <c r="C178">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>192</v>
+      </c>
+      <c r="B179" t="s">
+        <v>781</v>
+      </c>
+      <c r="C179">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>562</v>
+      </c>
+      <c r="B180" t="s">
+        <v>782</v>
+      </c>
+      <c r="C180">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>451</v>
+      </c>
+      <c r="B181" t="s">
+        <v>783</v>
+      </c>
+      <c r="C181">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>121</v>
+      </c>
+      <c r="B182" t="s">
+        <v>784</v>
+      </c>
+      <c r="C182">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>5</v>
+      </c>
+      <c r="B183" t="s">
+        <v>785</v>
+      </c>
+      <c r="C183">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>346</v>
+      </c>
+      <c r="B184" t="s">
+        <v>786</v>
+      </c>
+      <c r="C184">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>257</v>
+      </c>
+      <c r="B185" t="s">
+        <v>787</v>
+      </c>
+      <c r="C185">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>373</v>
+      </c>
+      <c r="B186" t="s">
+        <v>788</v>
+      </c>
+      <c r="C186">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>98</v>
+      </c>
+      <c r="B187" t="s">
+        <v>789</v>
+      </c>
+      <c r="C187">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>506</v>
+      </c>
+      <c r="B188" t="s">
+        <v>790</v>
+      </c>
+      <c r="C188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>391</v>
+      </c>
+      <c r="B189" t="s">
+        <v>791</v>
+      </c>
+      <c r="C189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>273</v>
+      </c>
+      <c r="B190" t="s">
+        <v>792</v>
+      </c>
+      <c r="C190">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>468</v>
+      </c>
+      <c r="B191" t="s">
+        <v>793</v>
+      </c>
+      <c r="C191">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>204</v>
+      </c>
+      <c r="B192" t="s">
+        <v>794</v>
+      </c>
+      <c r="C192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>100</v>
+      </c>
+      <c r="B193" t="s">
+        <v>795</v>
+      </c>
+      <c r="C193">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>6</v>
+      </c>
+      <c r="B194" t="s">
+        <v>796</v>
+      </c>
+      <c r="C194">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>361</v>
+      </c>
+      <c r="B195" t="s">
+        <v>797</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>252</v>
+      </c>
+      <c r="B196" t="s">
+        <v>798</v>
+      </c>
+      <c r="C196">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>108</v>
+      </c>
+      <c r="B197" t="s">
+        <v>799</v>
+      </c>
+      <c r="C197">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>500</v>
+      </c>
+      <c r="B198" t="s">
+        <v>800</v>
+      </c>
+      <c r="C198">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>354</v>
+      </c>
+      <c r="B199" t="s">
+        <v>801</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>456</v>
+      </c>
+      <c r="B200" t="s">
+        <v>802</v>
+      </c>
+      <c r="C200">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>417</v>
+      </c>
+      <c r="B201" t="s">
+        <v>803</v>
+      </c>
+      <c r="C201">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>308</v>
+      </c>
+      <c r="B202" t="s">
+        <v>804</v>
+      </c>
+      <c r="C202">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>563</v>
+      </c>
+      <c r="B203" t="s">
+        <v>805</v>
+      </c>
+      <c r="C203">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>244</v>
+      </c>
+      <c r="B204" t="s">
+        <v>806</v>
+      </c>
+      <c r="C204">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>561</v>
+      </c>
+      <c r="B205" t="s">
+        <v>807</v>
+      </c>
+      <c r="C205">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>50</v>
+      </c>
+      <c r="B206" t="s">
+        <v>808</v>
+      </c>
+      <c r="C206">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>385</v>
+      </c>
+      <c r="B207" t="s">
+        <v>809</v>
+      </c>
+      <c r="C207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>442</v>
+      </c>
+      <c r="B208" t="s">
+        <v>810</v>
+      </c>
+      <c r="C208">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>49</v>
+      </c>
+      <c r="B209" t="s">
+        <v>811</v>
+      </c>
+      <c r="C209">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>557</v>
+      </c>
+      <c r="B210" t="s">
+        <v>812</v>
+      </c>
+      <c r="C210">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>255</v>
+      </c>
+      <c r="B211" t="s">
+        <v>813</v>
+      </c>
+      <c r="C211">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>343</v>
+      </c>
+      <c r="B212" t="s">
+        <v>814</v>
+      </c>
+      <c r="C212">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>207</v>
+      </c>
+      <c r="B213" t="s">
+        <v>815</v>
+      </c>
+      <c r="C213">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>62</v>
+      </c>
+      <c r="B214" t="s">
+        <v>816</v>
+      </c>
+      <c r="C214">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>201</v>
+      </c>
+      <c r="B215" t="s">
+        <v>817</v>
+      </c>
+      <c r="C215">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>12</v>
+      </c>
+      <c r="B216" t="s">
+        <v>818</v>
+      </c>
+      <c r="C216">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>224</v>
+      </c>
+      <c r="B217" t="s">
+        <v>819</v>
+      </c>
+      <c r="C217">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>225</v>
+      </c>
+      <c r="B218" t="s">
+        <v>820</v>
+      </c>
+      <c r="C218">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>543</v>
+      </c>
+      <c r="B219" t="s">
+        <v>821</v>
+      </c>
+      <c r="C219">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>80</v>
+      </c>
+      <c r="B220" t="s">
+        <v>822</v>
+      </c>
+      <c r="C220">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>471</v>
+      </c>
+      <c r="B221" t="s">
+        <v>823</v>
+      </c>
+      <c r="C221">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>11</v>
+      </c>
+      <c r="B222" t="s">
+        <v>824</v>
+      </c>
+      <c r="C222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>104</v>
+      </c>
+      <c r="B223" t="s">
+        <v>825</v>
+      </c>
+      <c r="C223">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>23</v>
+      </c>
+      <c r="B224" t="s">
+        <v>826</v>
+      </c>
+      <c r="C224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>55</v>
+      </c>
+      <c r="B225" t="s">
+        <v>827</v>
+      </c>
+      <c r="C225">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>226</v>
+      </c>
+      <c r="B226" t="s">
+        <v>828</v>
+      </c>
+      <c r="C226">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>153</v>
+      </c>
+      <c r="B227" t="s">
+        <v>829</v>
+      </c>
+      <c r="C227">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>490</v>
+      </c>
+      <c r="B228" t="s">
+        <v>830</v>
+      </c>
+      <c r="C228">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>592</v>
+      </c>
+      <c r="B229" t="s">
+        <v>831</v>
+      </c>
+      <c r="C229">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>383</v>
+      </c>
+      <c r="B230" t="s">
+        <v>832</v>
+      </c>
+      <c r="C230">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>494</v>
+      </c>
+      <c r="B231" t="s">
+        <v>833</v>
+      </c>
+      <c r="C231">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>514</v>
+      </c>
+      <c r="B232" t="s">
+        <v>834</v>
+      </c>
+      <c r="C232">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>566</v>
+      </c>
+      <c r="B233" t="s">
+        <v>835</v>
+      </c>
+      <c r="C233">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>579</v>
+      </c>
+      <c r="B234" t="s">
+        <v>836</v>
+      </c>
+      <c r="C234">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>328</v>
+      </c>
+      <c r="B235" t="s">
+        <v>837</v>
+      </c>
+      <c r="C235">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>393</v>
+      </c>
+      <c r="B236" t="s">
+        <v>838</v>
+      </c>
+      <c r="C236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>266</v>
+      </c>
+      <c r="B237" t="s">
+        <v>839</v>
+      </c>
+      <c r="C237">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>388</v>
+      </c>
+      <c r="B238" t="s">
+        <v>840</v>
+      </c>
+      <c r="C238">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>227</v>
+      </c>
+      <c r="B239" t="s">
+        <v>841</v>
+      </c>
+      <c r="C239">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>457</v>
+      </c>
+      <c r="B240" t="s">
+        <v>842</v>
+      </c>
+      <c r="C240">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>95</v>
+      </c>
+      <c r="B241" t="s">
+        <v>843</v>
+      </c>
+      <c r="C241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>61</v>
+      </c>
+      <c r="B242" t="s">
+        <v>844</v>
+      </c>
+      <c r="C242">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>582</v>
+      </c>
+      <c r="B243" t="s">
+        <v>845</v>
+      </c>
+      <c r="C243">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>503</v>
+      </c>
+      <c r="B244" t="s">
+        <v>846</v>
+      </c>
+      <c r="C244">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>426</v>
+      </c>
+      <c r="B245" t="s">
+        <v>847</v>
+      </c>
+      <c r="C245">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>65</v>
+      </c>
+      <c r="B246" t="s">
+        <v>848</v>
+      </c>
+      <c r="C246">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>141</v>
+      </c>
+      <c r="B247" t="s">
+        <v>849</v>
+      </c>
+      <c r="C247">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>476</v>
+      </c>
+      <c r="B248" t="s">
+        <v>850</v>
+      </c>
+      <c r="C248">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>64</v>
+      </c>
+      <c r="B249" t="s">
+        <v>851</v>
+      </c>
+      <c r="C249">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>444</v>
+      </c>
+      <c r="B250" t="s">
+        <v>852</v>
+      </c>
+      <c r="C250">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>583</v>
+      </c>
+      <c r="B251" t="s">
+        <v>853</v>
+      </c>
+      <c r="C251">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>569</v>
+      </c>
+      <c r="B252" t="s">
+        <v>854</v>
+      </c>
+      <c r="C252">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>483</v>
+      </c>
+      <c r="B253" t="s">
+        <v>855</v>
+      </c>
+      <c r="C253">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>475</v>
+      </c>
+      <c r="B254" t="s">
+        <v>856</v>
+      </c>
+      <c r="C254">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>220</v>
+      </c>
+      <c r="B255" t="s">
+        <v>857</v>
+      </c>
+      <c r="C255">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>473</v>
+      </c>
+      <c r="B256" t="s">
+        <v>858</v>
+      </c>
+      <c r="C256">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>191</v>
+      </c>
+      <c r="B257" t="s">
+        <v>859</v>
+      </c>
+      <c r="C257">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>439</v>
+      </c>
+      <c r="B258" t="s">
+        <v>860</v>
+      </c>
+      <c r="C258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>293</v>
+      </c>
+      <c r="B259" t="s">
+        <v>861</v>
+      </c>
+      <c r="C259">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>465</v>
+      </c>
+      <c r="B260" t="s">
+        <v>862</v>
+      </c>
+      <c r="C260">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>546</v>
+      </c>
+      <c r="B261" t="s">
+        <v>863</v>
+      </c>
+      <c r="C261">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>211</v>
+      </c>
+      <c r="B262" t="s">
+        <v>864</v>
+      </c>
+      <c r="C262">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>233</v>
+      </c>
+      <c r="B263" t="s">
+        <v>865</v>
+      </c>
+      <c r="C263">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>271</v>
+      </c>
+      <c r="B264" t="s">
+        <v>866</v>
+      </c>
+      <c r="C264">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>538</v>
+      </c>
+      <c r="B265" t="s">
+        <v>867</v>
+      </c>
+      <c r="C265">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>407</v>
+      </c>
+      <c r="B266" t="s">
+        <v>868</v>
+      </c>
+      <c r="C266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>92</v>
+      </c>
+      <c r="B267" t="s">
+        <v>869</v>
+      </c>
+      <c r="C267">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>389</v>
+      </c>
+      <c r="B268" t="s">
+        <v>870</v>
+      </c>
+      <c r="C268">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>520</v>
+      </c>
+      <c r="B269" t="s">
+        <v>871</v>
+      </c>
+      <c r="C269">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>418</v>
+      </c>
+      <c r="B270" t="s">
+        <v>872</v>
+      </c>
+      <c r="C270">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>319</v>
+      </c>
+      <c r="B271" t="s">
+        <v>873</v>
+      </c>
+      <c r="C271">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>556</v>
+      </c>
+      <c r="B272" t="s">
+        <v>874</v>
+      </c>
+      <c r="C272">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>301</v>
+      </c>
+      <c r="B273" t="s">
+        <v>875</v>
+      </c>
+      <c r="C273">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>284</v>
+      </c>
+      <c r="B274" t="s">
+        <v>876</v>
+      </c>
+      <c r="C274">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>46</v>
+      </c>
+      <c r="B275" t="s">
+        <v>877</v>
+      </c>
+      <c r="C275">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>512</v>
+      </c>
+      <c r="B276" t="s">
+        <v>878</v>
+      </c>
+      <c r="C276">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>331</v>
+      </c>
+      <c r="B277" t="s">
+        <v>879</v>
+      </c>
+      <c r="C277">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>507</v>
+      </c>
+      <c r="B278" t="s">
+        <v>880</v>
+      </c>
+      <c r="C278">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>115</v>
+      </c>
+      <c r="B279" t="s">
+        <v>881</v>
+      </c>
+      <c r="C279">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>250</v>
+      </c>
+      <c r="B280" t="s">
+        <v>882</v>
+      </c>
+      <c r="C280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>454</v>
+      </c>
+      <c r="B281" t="s">
+        <v>883</v>
+      </c>
+      <c r="C281">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>34</v>
+      </c>
+      <c r="B282" t="s">
+        <v>884</v>
+      </c>
+      <c r="C282">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>297</v>
+      </c>
+      <c r="B283" t="s">
+        <v>885</v>
+      </c>
+      <c r="C283">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>261</v>
+      </c>
+      <c r="B284" t="s">
+        <v>886</v>
+      </c>
+      <c r="C284">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>542</v>
+      </c>
+      <c r="B285" t="s">
+        <v>887</v>
+      </c>
+      <c r="C285">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>72</v>
+      </c>
+      <c r="B286" t="s">
+        <v>888</v>
+      </c>
+      <c r="C286">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>541</v>
+      </c>
+      <c r="B287" t="s">
+        <v>889</v>
+      </c>
+      <c r="C287">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>93</v>
+      </c>
+      <c r="B288" t="s">
+        <v>890</v>
+      </c>
+      <c r="C288">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>196</v>
+      </c>
+      <c r="B289" t="s">
+        <v>891</v>
+      </c>
+      <c r="C289">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>580</v>
+      </c>
+      <c r="B290" t="s">
+        <v>892</v>
+      </c>
+      <c r="C290">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>321</v>
+      </c>
+      <c r="B291" t="s">
+        <v>893</v>
+      </c>
+      <c r="C291">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>356</v>
+      </c>
+      <c r="B292" t="s">
+        <v>894</v>
+      </c>
+      <c r="C292">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>405</v>
+      </c>
+      <c r="B293" t="s">
+        <v>895</v>
+      </c>
+      <c r="C293">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>326</v>
+      </c>
+      <c r="B294" t="s">
+        <v>896</v>
+      </c>
+      <c r="C294">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>386</v>
+      </c>
+      <c r="B295" t="s">
+        <v>897</v>
+      </c>
+      <c r="C295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>482</v>
+      </c>
+      <c r="B296" t="s">
+        <v>898</v>
+      </c>
+      <c r="C296">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>286</v>
+      </c>
+      <c r="B297" t="s">
+        <v>899</v>
+      </c>
+      <c r="C297">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>279</v>
+      </c>
+      <c r="B298" t="s">
+        <v>900</v>
+      </c>
+      <c r="C298">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>466</v>
+      </c>
+      <c r="B299" t="s">
+        <v>901</v>
+      </c>
+      <c r="C299">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>305</v>
+      </c>
+      <c r="B300" t="s">
+        <v>902</v>
+      </c>
+      <c r="C300">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>577</v>
+      </c>
+      <c r="B301" t="s">
+        <v>903</v>
+      </c>
+      <c r="C301">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>435</v>
+      </c>
+      <c r="B302" t="s">
+        <v>904</v>
+      </c>
+      <c r="C302">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>564</v>
+      </c>
+      <c r="B303" t="s">
+        <v>905</v>
+      </c>
+      <c r="C303">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>290</v>
+      </c>
+      <c r="B304" t="s">
+        <v>906</v>
+      </c>
+      <c r="C304">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>159</v>
+      </c>
+      <c r="B305" t="s">
+        <v>907</v>
+      </c>
+      <c r="C305">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>4</v>
+      </c>
+      <c r="B306" t="s">
+        <v>908</v>
+      </c>
+      <c r="C306">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>555</v>
+      </c>
+      <c r="B307" t="s">
+        <v>909</v>
+      </c>
+      <c r="C307">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>437</v>
+      </c>
+      <c r="B308" t="s">
+        <v>910</v>
+      </c>
+      <c r="C308">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>262</v>
+      </c>
+      <c r="B309" t="s">
+        <v>911</v>
+      </c>
+      <c r="C309">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>113</v>
+      </c>
+      <c r="B310" t="s">
+        <v>912</v>
+      </c>
+      <c r="C310">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>423</v>
+      </c>
+      <c r="B311" t="s">
+        <v>913</v>
+      </c>
+      <c r="C311">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>218</v>
+      </c>
+      <c r="B312" t="s">
+        <v>914</v>
+      </c>
+      <c r="C312">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>26</v>
+      </c>
+      <c r="B313" t="s">
+        <v>915</v>
+      </c>
+      <c r="C313">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>260</v>
+      </c>
+      <c r="B314" t="s">
+        <v>916</v>
+      </c>
+      <c r="C314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>123</v>
+      </c>
+      <c r="B315" t="s">
+        <v>917</v>
+      </c>
+      <c r="C315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>472</v>
+      </c>
+      <c r="B316" t="s">
+        <v>918</v>
+      </c>
+      <c r="C316">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>242</v>
+      </c>
+      <c r="B317" t="s">
+        <v>919</v>
+      </c>
+      <c r="C317">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>424</v>
+      </c>
+      <c r="B318" t="s">
+        <v>920</v>
+      </c>
+      <c r="C318">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>152</v>
+      </c>
+      <c r="B319" t="s">
+        <v>921</v>
+      </c>
+      <c r="C319">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>316</v>
+      </c>
+      <c r="B320" t="s">
+        <v>922</v>
+      </c>
+      <c r="C320">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>169</v>
+      </c>
+      <c r="B321" t="s">
+        <v>923</v>
+      </c>
+      <c r="C321">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>589</v>
+      </c>
+      <c r="B322" t="s">
+        <v>924</v>
+      </c>
+      <c r="C322">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>57</v>
+      </c>
+      <c r="B323" t="s">
+        <v>925</v>
+      </c>
+      <c r="C323">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>131</v>
+      </c>
+      <c r="B324" t="s">
+        <v>926</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>455</v>
+      </c>
+      <c r="B325" t="s">
+        <v>927</v>
+      </c>
+      <c r="C325">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>135</v>
+      </c>
+      <c r="B326" t="s">
+        <v>928</v>
+      </c>
+      <c r="C326">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>510</v>
+      </c>
+      <c r="B327" t="s">
+        <v>929</v>
+      </c>
+      <c r="C327">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>10</v>
+      </c>
+      <c r="B328" t="s">
+        <v>930</v>
+      </c>
+      <c r="C328">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>68</v>
+      </c>
+      <c r="B329" t="s">
+        <v>931</v>
+      </c>
+      <c r="C329">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A330" t="s">
+        <v>158</v>
+      </c>
+      <c r="B330" t="s">
+        <v>932</v>
+      </c>
+      <c r="C330">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A331" t="s">
+        <v>551</v>
+      </c>
+      <c r="B331" t="s">
+        <v>933</v>
+      </c>
+      <c r="C331">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A332" t="s">
+        <v>519</v>
+      </c>
+      <c r="B332" t="s">
+        <v>934</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A333" t="s">
+        <v>492</v>
+      </c>
+      <c r="B333" t="s">
+        <v>935</v>
+      </c>
+      <c r="C333">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A334" t="s">
+        <v>58</v>
+      </c>
+      <c r="B334" t="s">
+        <v>936</v>
+      </c>
+      <c r="C334">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A335" t="s">
+        <v>28</v>
+      </c>
+      <c r="B335" t="s">
+        <v>937</v>
+      </c>
+      <c r="C335">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A336" t="s">
+        <v>281</v>
+      </c>
+      <c r="B336" t="s">
+        <v>938</v>
+      </c>
+      <c r="C336">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A337" t="s">
+        <v>552</v>
+      </c>
+      <c r="B337" t="s">
+        <v>939</v>
+      </c>
+      <c r="C337">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>265</v>
+      </c>
+      <c r="B338" t="s">
+        <v>940</v>
+      </c>
+      <c r="C338">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A339" t="s">
+        <v>412</v>
+      </c>
+      <c r="B339" t="s">
+        <v>941</v>
+      </c>
+      <c r="C339">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A340" t="s">
+        <v>59</v>
+      </c>
+      <c r="B340" t="s">
+        <v>942</v>
+      </c>
+      <c r="C340">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A341" t="s">
+        <v>73</v>
+      </c>
+      <c r="B341" t="s">
+        <v>943</v>
+      </c>
+      <c r="C341">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>370</v>
+      </c>
+      <c r="B342" t="s">
+        <v>944</v>
+      </c>
+      <c r="C342">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A343" t="s">
+        <v>529</v>
+      </c>
+      <c r="B343" t="s">
+        <v>945</v>
+      </c>
+      <c r="C343">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>432</v>
+      </c>
+      <c r="B344" t="s">
+        <v>946</v>
+      </c>
+      <c r="C344">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A345" t="s">
+        <v>111</v>
+      </c>
+      <c r="B345" t="s">
+        <v>947</v>
+      </c>
+      <c r="C345">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A346" t="s">
+        <v>112</v>
+      </c>
+      <c r="B346" t="s">
+        <v>948</v>
+      </c>
+      <c r="C346">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A347" t="s">
+        <v>97</v>
+      </c>
+      <c r="B347" t="s">
+        <v>949</v>
+      </c>
+      <c r="C347">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A348" t="s">
+        <v>528</v>
+      </c>
+      <c r="B348" t="s">
+        <v>950</v>
+      </c>
+      <c r="C348">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A349" t="s">
+        <v>469</v>
+      </c>
+      <c r="B349" t="s">
+        <v>951</v>
+      </c>
+      <c r="C349">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A350" t="s">
+        <v>334</v>
+      </c>
+      <c r="B350" t="s">
+        <v>952</v>
+      </c>
+      <c r="C350">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A351" t="s">
+        <v>185</v>
+      </c>
+      <c r="B351" t="s">
+        <v>953</v>
+      </c>
+      <c r="C351">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A352" t="s">
+        <v>333</v>
+      </c>
+      <c r="B352" t="s">
+        <v>954</v>
+      </c>
+      <c r="C352">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A353" t="s">
+        <v>221</v>
+      </c>
+      <c r="B353" t="s">
+        <v>955</v>
+      </c>
+      <c r="C353">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A354" t="s">
+        <v>37</v>
+      </c>
+      <c r="B354" t="s">
+        <v>956</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A355" t="s">
+        <v>526</v>
+      </c>
+      <c r="B355" t="s">
+        <v>957</v>
+      </c>
+      <c r="C355">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A356" t="s">
+        <v>208</v>
+      </c>
+      <c r="B356" t="s">
+        <v>958</v>
+      </c>
+      <c r="C356">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A357" t="s">
+        <v>535</v>
+      </c>
+      <c r="B357" t="s">
+        <v>959</v>
+      </c>
+      <c r="C357">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A358" t="s">
+        <v>458</v>
+      </c>
+      <c r="B358" t="s">
+        <v>960</v>
+      </c>
+      <c r="C358">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A359" t="s">
+        <v>69</v>
+      </c>
+      <c r="B359" t="s">
+        <v>961</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A360" t="s">
+        <v>368</v>
+      </c>
+      <c r="B360" t="s">
+        <v>962</v>
+      </c>
+      <c r="C360">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A361" t="s">
+        <v>497</v>
+      </c>
+      <c r="B361" t="s">
+        <v>963</v>
+      </c>
+      <c r="C361">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A362" t="s">
+        <v>517</v>
+      </c>
+      <c r="B362" t="s">
+        <v>964</v>
+      </c>
+      <c r="C362">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A363" t="s">
+        <v>323</v>
+      </c>
+      <c r="B363" t="s">
+        <v>965</v>
+      </c>
+      <c r="C363">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>150</v>
+      </c>
+      <c r="B364" t="s">
+        <v>966</v>
+      </c>
+      <c r="C364">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A365" t="s">
+        <v>554</v>
+      </c>
+      <c r="B365" t="s">
+        <v>967</v>
+      </c>
+      <c r="C365">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>518</v>
+      </c>
+      <c r="B366" t="s">
+        <v>968</v>
+      </c>
+      <c r="C366">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>485</v>
+      </c>
+      <c r="B367" t="s">
+        <v>969</v>
+      </c>
+      <c r="C367">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>550</v>
+      </c>
+      <c r="B368" t="s">
+        <v>970</v>
+      </c>
+      <c r="C368">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>352</v>
+      </c>
+      <c r="B369" t="s">
+        <v>971</v>
+      </c>
+      <c r="C369">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>94</v>
+      </c>
+      <c r="B370" t="s">
+        <v>972</v>
+      </c>
+      <c r="C370">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>314</v>
+      </c>
+      <c r="B371" t="s">
+        <v>973</v>
+      </c>
+      <c r="C371">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>198</v>
+      </c>
+      <c r="B372" t="s">
+        <v>974</v>
+      </c>
+      <c r="C372">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>313</v>
+      </c>
+      <c r="B373" t="s">
+        <v>975</v>
+      </c>
+      <c r="C373">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>349</v>
+      </c>
+      <c r="B374" t="s">
+        <v>976</v>
+      </c>
+      <c r="C374">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>45</v>
+      </c>
+      <c r="B375" t="s">
+        <v>977</v>
+      </c>
+      <c r="C375">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>524</v>
+      </c>
+      <c r="B376" t="s">
+        <v>978</v>
+      </c>
+      <c r="C376">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>422</v>
+      </c>
+      <c r="B377" t="s">
+        <v>979</v>
+      </c>
+      <c r="C377">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>103</v>
+      </c>
+      <c r="B378" t="s">
+        <v>980</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>360</v>
+      </c>
+      <c r="B379" t="s">
+        <v>981</v>
+      </c>
+      <c r="C379">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A380" t="s">
+        <v>128</v>
+      </c>
+      <c r="B380" t="s">
+        <v>982</v>
+      </c>
+      <c r="C380">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A381" t="s">
+        <v>182</v>
+      </c>
+      <c r="B381" t="s">
+        <v>983</v>
+      </c>
+      <c r="C381">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A382" t="s">
+        <v>67</v>
+      </c>
+      <c r="B382" t="s">
+        <v>984</v>
+      </c>
+      <c r="C382">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A383" t="s">
+        <v>516</v>
+      </c>
+      <c r="B383" t="s">
+        <v>985</v>
+      </c>
+      <c r="C383">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A384" t="s">
+        <v>317</v>
+      </c>
+      <c r="B384" t="s">
+        <v>986</v>
+      </c>
+      <c r="C384">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A385" t="s">
+        <v>591</v>
+      </c>
+      <c r="B385" t="s">
+        <v>987</v>
+      </c>
+      <c r="C385">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A386" t="s">
+        <v>14</v>
+      </c>
+      <c r="B386" t="s">
+        <v>988</v>
+      </c>
+      <c r="C386">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A387" t="s">
+        <v>32</v>
+      </c>
+      <c r="B387" t="s">
+        <v>989</v>
+      </c>
+      <c r="C387">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A388" t="s">
+        <v>222</v>
+      </c>
+      <c r="B388" t="s">
+        <v>990</v>
+      </c>
+      <c r="C388">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A389" t="s">
+        <v>234</v>
+      </c>
+      <c r="B389" t="s">
+        <v>991</v>
+      </c>
+      <c r="C389">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A390" t="s">
+        <v>479</v>
+      </c>
+      <c r="B390" t="s">
+        <v>992</v>
+      </c>
+      <c r="C390">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A391" t="s">
+        <v>38</v>
+      </c>
+      <c r="B391" t="s">
+        <v>993</v>
+      </c>
+      <c r="C391">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A392" t="s">
+        <v>372</v>
+      </c>
+      <c r="B392" t="s">
+        <v>994</v>
+      </c>
+      <c r="C392">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A393" t="s">
+        <v>462</v>
+      </c>
+      <c r="B393" t="s">
+        <v>995</v>
+      </c>
+      <c r="C393">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A394" t="s">
+        <v>54</v>
+      </c>
+      <c r="B394" t="s">
+        <v>996</v>
+      </c>
+      <c r="C394">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A395" t="s">
+        <v>146</v>
+      </c>
+      <c r="B395" t="s">
+        <v>997</v>
+      </c>
+      <c r="C395">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A396" t="s">
+        <v>292</v>
+      </c>
+      <c r="B396" t="s">
+        <v>998</v>
+      </c>
+      <c r="C396">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A397" t="s">
+        <v>189</v>
+      </c>
+      <c r="B397" t="s">
+        <v>999</v>
+      </c>
+      <c r="C397">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A398" t="s">
+        <v>523</v>
+      </c>
+      <c r="B398" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A399" t="s">
+        <v>124</v>
+      </c>
+      <c r="B399" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C399">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A400" t="s">
+        <v>140</v>
+      </c>
+      <c r="B400" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C400">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A401" t="s">
+        <v>390</v>
+      </c>
+      <c r="B401" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C401">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A402" t="s">
+        <v>463</v>
+      </c>
+      <c r="B402" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C402">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A403" t="s">
+        <v>409</v>
+      </c>
+      <c r="B403" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C403">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A404" t="s">
+        <v>31</v>
+      </c>
+      <c r="B404" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C404">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A405" t="s">
+        <v>575</v>
+      </c>
+      <c r="B405" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C405">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A406" t="s">
+        <v>380</v>
+      </c>
+      <c r="B406" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C406">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A407" t="s">
+        <v>585</v>
+      </c>
+      <c r="B407" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C407">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A408" t="s">
+        <v>173</v>
+      </c>
+      <c r="B408" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C408">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A409" t="s">
+        <v>63</v>
+      </c>
+      <c r="B409" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C409">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A410" t="s">
+        <v>216</v>
+      </c>
+      <c r="B410" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C410">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A411" t="s">
+        <v>311</v>
+      </c>
+      <c r="B411" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C411">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A412" t="s">
+        <v>186</v>
+      </c>
+      <c r="B412" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C412">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A413" t="s">
+        <v>137</v>
+      </c>
+      <c r="B413" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C413">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A414" t="s">
+        <v>83</v>
+      </c>
+      <c r="B414" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C414">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A415" t="s">
+        <v>384</v>
+      </c>
+      <c r="B415" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C415">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A416" t="s">
+        <v>341</v>
+      </c>
+      <c r="B416" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C416">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A417" t="s">
+        <v>578</v>
+      </c>
+      <c r="B417" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C417">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A418" t="s">
+        <v>365</v>
+      </c>
+      <c r="B418" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C418">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A419" t="s">
+        <v>549</v>
+      </c>
+      <c r="B419" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C419">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A420" t="s">
+        <v>203</v>
+      </c>
+      <c r="B420" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C420">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>586</v>
+      </c>
+      <c r="B421" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C421">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A422" t="s">
+        <v>527</v>
+      </c>
+      <c r="B422" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C422">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
+        <v>565</v>
+      </c>
+      <c r="B423" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C423">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
+        <v>41</v>
+      </c>
+      <c r="B424" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C424">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A425" t="s">
+        <v>197</v>
+      </c>
+      <c r="B425" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A426" t="s">
+        <v>324</v>
+      </c>
+      <c r="B426" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C426">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A427" t="s">
+        <v>364</v>
+      </c>
+      <c r="B427" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C427">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A428" t="s">
+        <v>595</v>
+      </c>
+      <c r="B428" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C428">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A429" t="s">
+        <v>403</v>
+      </c>
+      <c r="B429" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C429">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A430" t="s">
+        <v>161</v>
+      </c>
+      <c r="B430" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C430">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A431" t="s">
+        <v>358</v>
+      </c>
+      <c r="B431" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C431">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A432" t="s">
+        <v>171</v>
+      </c>
+      <c r="B432" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C432">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A433" t="s">
+        <v>241</v>
+      </c>
+      <c r="B433" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C433">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A434" t="s">
+        <v>1</v>
+      </c>
+      <c r="B434" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C434">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A435" t="s">
+        <v>484</v>
+      </c>
+      <c r="B435" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C435">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A436" t="s">
+        <v>396</v>
+      </c>
+      <c r="B436" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C436">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A437" t="s">
+        <v>202</v>
+      </c>
+      <c r="B437" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C437">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A438" t="s">
+        <v>232</v>
+      </c>
+      <c r="B438" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C438">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A439" t="s">
+        <v>139</v>
+      </c>
+      <c r="B439" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C439">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A440" t="s">
+        <v>156</v>
+      </c>
+      <c r="B440" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C440">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A441" t="s">
+        <v>251</v>
+      </c>
+      <c r="B441" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C441">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A442" t="s">
+        <v>56</v>
+      </c>
+      <c r="B442" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C442">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A443" t="s">
+        <v>291</v>
+      </c>
+      <c r="B443" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C443">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A444" t="s">
+        <v>43</v>
+      </c>
+      <c r="B444" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C444">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A445" t="s">
+        <v>116</v>
+      </c>
+      <c r="B445" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C445">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A446" t="s">
+        <v>7</v>
+      </c>
+      <c r="B446" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C446">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A447" t="s">
+        <v>544</v>
+      </c>
+      <c r="B447" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C447">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A448" t="s">
+        <v>329</v>
+      </c>
+      <c r="B448" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C448">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A449" t="s">
+        <v>76</v>
+      </c>
+      <c r="B449" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C449">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A450" t="s">
+        <v>39</v>
+      </c>
+      <c r="B450" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C450">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A451" t="s">
+        <v>160</v>
+      </c>
+      <c r="B451" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C451">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A452" t="s">
+        <v>315</v>
+      </c>
+      <c r="B452" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C452">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A453" t="s">
+        <v>350</v>
+      </c>
+      <c r="B453" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C453">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A454" t="s">
+        <v>268</v>
+      </c>
+      <c r="B454" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C454">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A455" t="s">
+        <v>164</v>
+      </c>
+      <c r="B455" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C455">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A456" t="s">
+        <v>306</v>
+      </c>
+      <c r="B456" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C456">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A457" t="s">
+        <v>109</v>
+      </c>
+      <c r="B457" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C457">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A458" t="s">
+        <v>501</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C458">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A459" t="s">
+        <v>84</v>
+      </c>
+      <c r="B459" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C459">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A460" t="s">
+        <v>13</v>
+      </c>
+      <c r="B460" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C460">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A461" t="s">
+        <v>399</v>
+      </c>
+      <c r="B461" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C461">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A462" t="s">
+        <v>247</v>
+      </c>
+      <c r="B462" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C462">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A463" t="s">
+        <v>2</v>
+      </c>
+      <c r="B463" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C463">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A464" t="s">
+        <v>298</v>
+      </c>
+      <c r="B464" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C464">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A465" t="s">
+        <v>118</v>
+      </c>
+      <c r="B465" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C465">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A466" t="s">
+        <v>18</v>
+      </c>
+      <c r="B466" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C466">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A467" t="s">
+        <v>172</v>
+      </c>
+      <c r="B467" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C467">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A468" t="s">
+        <v>493</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C468">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A469" t="s">
+        <v>280</v>
+      </c>
+      <c r="B469" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C469">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A470" t="s">
+        <v>598</v>
+      </c>
+      <c r="B470" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C470">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A471" t="s">
+        <v>21</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C471">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A472" t="s">
+        <v>177</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C472">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A473" t="s">
+        <v>248</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C473">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A474" t="s">
+        <v>496</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C474">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A475" t="s">
+        <v>487</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C475">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A476" t="s">
+        <v>20</v>
+      </c>
+      <c r="B476" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A477" t="s">
+        <v>154</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C477">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A478" t="s">
+        <v>513</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A479" t="s">
+        <v>19</v>
+      </c>
+      <c r="B479" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A480" t="s">
+        <v>22</v>
+      </c>
+      <c r="B480" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C480">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A481" t="s">
+        <v>342</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C481">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A482" t="s">
+        <v>35</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C482">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A483" t="s">
+        <v>205</v>
+      </c>
+      <c r="B483" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C483">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A484" t="s">
+        <v>33</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C484">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A485" t="s">
+        <v>249</v>
+      </c>
+      <c r="B485" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C485">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A486" t="s">
+        <v>464</v>
+      </c>
+      <c r="B486" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C486">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A487" t="s">
+        <v>338</v>
+      </c>
+      <c r="B487" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C487">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A488" t="s">
+        <v>142</v>
+      </c>
+      <c r="B488" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A489" t="s">
+        <v>237</v>
+      </c>
+      <c r="B489" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C489">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A490" t="s">
+        <v>330</v>
+      </c>
+      <c r="B490" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C490">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A491" t="s">
+        <v>522</v>
+      </c>
+      <c r="B491" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C491">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A492" t="s">
+        <v>42</v>
+      </c>
+      <c r="B492" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C492">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A493" t="s">
+        <v>371</v>
+      </c>
+      <c r="B493" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C493">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A494" t="s">
+        <v>369</v>
+      </c>
+      <c r="B494" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C494">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A495" t="s">
+        <v>379</v>
+      </c>
+      <c r="B495" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C495">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A496" t="s">
+        <v>376</v>
+      </c>
+      <c r="B496" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C496">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A497" t="s">
+        <v>339</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C497">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A498" t="s">
+        <v>213</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C498">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A499" t="s">
+        <v>285</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C499">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A500" t="s">
+        <v>212</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C500">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A501" t="s">
+        <v>303</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C501">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A502" t="s">
+        <v>240</v>
+      </c>
+      <c r="B502" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C502">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A503" t="s">
+        <v>209</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C503">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A504" t="s">
+        <v>461</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C504">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A505" t="s">
+        <v>238</v>
+      </c>
+      <c r="B505" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C505">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A506" t="s">
+        <v>60</v>
+      </c>
+      <c r="B506" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C506">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A507" t="s">
+        <v>533</v>
+      </c>
+      <c r="B507" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C507">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A508" t="s">
+        <v>193</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A509" t="s">
+        <v>144</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C509">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A510" t="s">
+        <v>132</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C510">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A511" t="s">
+        <v>138</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C511">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A512" t="s">
+        <v>187</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C512">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A513" t="s">
+        <v>162</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C513">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A514" t="s">
+        <v>91</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C514">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A515" t="s">
+        <v>79</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C515">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A516" t="s">
+        <v>87</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C516">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A517" t="s">
+        <v>136</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C517">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A518" t="s">
+        <v>127</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C518">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A519" t="s">
+        <v>114</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C519">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A520" t="s">
+        <v>126</v>
+      </c>
+      <c r="B520" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C520">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A521" t="s">
+        <v>106</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C521">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A522" t="s">
+        <v>96</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C522">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A523" t="s">
+        <v>398</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C523">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A524" t="s">
+        <v>78</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C524">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A525" t="s">
+        <v>53</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C525">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A526" t="s">
+        <v>105</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C526">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A527" t="s">
+        <v>88</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A528" t="s">
+        <v>89</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C528">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A529" t="s">
+        <v>90</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C529">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A530" t="s">
+        <v>443</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C530">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A531" t="s">
+        <v>397</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C531">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A532" t="s">
+        <v>81</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C532">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A533" t="s">
+        <v>85</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C533">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A534" t="s">
+        <v>70</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C534">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A535" t="s">
+        <v>86</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C535">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A536" t="s">
+        <v>381</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C536">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A537" t="s">
+        <v>71</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C537">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A538" t="s">
+        <v>51</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C538">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A539" t="s">
+        <v>394</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C539">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A540" t="s">
+        <v>47</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C540">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A541" t="s">
+        <v>44</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C541">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A542" t="s">
+        <v>382</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C542">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A543" t="s">
+        <v>387</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C543">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A544" t="s">
+        <v>414</v>
+      </c>
+      <c r="B544" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C544">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A545" t="s">
+        <v>400</v>
+      </c>
+      <c r="B545" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C545">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A546" t="s">
+        <v>401</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C546">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A547" t="s">
+        <v>540</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C547">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A548" t="s">
+        <v>425</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C548">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A549" t="s">
+        <v>430</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C549">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A550" t="s">
+        <v>408</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C550">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A551" t="s">
+        <v>410</v>
+      </c>
+      <c r="B551" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C551">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A552" t="s">
+        <v>416</v>
+      </c>
+      <c r="B552" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C552">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A553" t="s">
+        <v>428</v>
+      </c>
+      <c r="B553" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C553">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A554" t="s">
+        <v>450</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A555" t="s">
+        <v>453</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C555">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A556" t="s">
+        <v>597</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C556">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A557" t="s">
+        <v>467</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C557">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A558" t="s">
+        <v>460</v>
+      </c>
+      <c r="B558" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C558">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A559" t="s">
+        <v>593</v>
+      </c>
+      <c r="B559" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C559">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A560" t="s">
+        <v>574</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C560">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A561" t="s">
+        <v>553</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C561">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A562" t="s">
+        <v>530</v>
+      </c>
+      <c r="B562" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C562">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A563" t="s">
+        <v>509</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C563">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A564" t="s">
+        <v>560</v>
+      </c>
+      <c r="B564" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C564">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A565" t="s">
+        <v>536</v>
+      </c>
+      <c r="B565" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C565">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A566" t="s">
+        <v>537</v>
+      </c>
+      <c r="B566" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C566">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A567" t="s">
+        <v>521</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C567">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A568" t="s">
+        <v>498</v>
+      </c>
+      <c r="B568" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C568">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A569" t="s">
+        <v>489</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C569">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A570" t="s">
+        <v>495</v>
+      </c>
+      <c r="B570" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C570">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A571" t="s">
+        <v>502</v>
+      </c>
+      <c r="B571" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C571">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A572" t="s">
+        <v>259</v>
+      </c>
+      <c r="B572" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C572">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A573" t="s">
+        <v>143</v>
+      </c>
+      <c r="B573" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C573">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A574" t="s">
+        <v>133</v>
+      </c>
+      <c r="B574" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C574">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A575" t="s">
+        <v>309</v>
+      </c>
+      <c r="B575" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C575">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A576" t="s">
+        <v>312</v>
+      </c>
+      <c r="B576" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C576">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A577" t="s">
+        <v>395</v>
+      </c>
+      <c r="B577" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C577">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A578" t="s">
+        <v>190</v>
+      </c>
+      <c r="B578" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C578">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A579" t="s">
+        <v>296</v>
+      </c>
+      <c r="B579" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C579">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A580" t="s">
+        <v>294</v>
+      </c>
+      <c r="B580" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C580">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A581" t="s">
+        <v>245</v>
+      </c>
+      <c r="B581" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C581">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A582" t="s">
+        <v>148</v>
+      </c>
+      <c r="B582" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C582">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A583" t="s">
+        <v>283</v>
+      </c>
+      <c r="B583" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C583">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A584" t="s">
+        <v>363</v>
+      </c>
+      <c r="B584" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C584">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A585" t="s">
+        <v>77</v>
+      </c>
+      <c r="B585" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C585">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A586" t="s">
+        <v>491</v>
+      </c>
+      <c r="B586" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C586">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A587" t="s">
+        <v>299</v>
+      </c>
+      <c r="B587" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C587">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A588" t="s">
+        <v>243</v>
+      </c>
+      <c r="B588" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C588">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A589" t="s">
+        <v>206</v>
+      </c>
+      <c r="B589" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C589">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A590" t="s">
+        <v>253</v>
+      </c>
+      <c r="B590" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C590">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A591" t="s">
+        <v>263</v>
+      </c>
+      <c r="B591" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C591">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A592" t="s">
+        <v>573</v>
+      </c>
+      <c r="B592" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C592">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A593" t="s">
+        <v>272</v>
+      </c>
+      <c r="B593" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C593">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A594" t="s">
+        <v>223</v>
+      </c>
+      <c r="B594" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C594">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A595" t="s">
+        <v>332</v>
+      </c>
+      <c r="B595" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C595">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A596" t="s">
+        <v>99</v>
+      </c>
+      <c r="B596" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C596">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A597" t="s">
+        <v>24</v>
+      </c>
+      <c r="B597" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C597">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A598" t="s">
+        <v>183</v>
+      </c>
+      <c r="B598" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C598">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A599" t="s">
+        <v>359</v>
+      </c>
+      <c r="B599" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C599">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист2"/>
   <dimension ref="A1:C611"/>
@@ -15953,25 +22603,25 @@
   </sheetData>
   <autoFilter ref="A1:C611"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A599 A612:A1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A600:A607">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A608:A609">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A610:A611">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист3"/>
   <dimension ref="A1:C600"/>
@@ -20925,13 +27575,13 @@
   </sheetData>
   <autoFilter ref="A1:C600"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A599 A601:A1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A600">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
